--- a/Сводная_таблица_автоворонок.xlsx
+++ b/Сводная_таблица_автоворонок.xlsx
@@ -8902,11 +8902,7 @@
 cvc_rsya_date = #{current_date}</t>
         </is>
       </c>
-      <c r="N262" s="7" t="inlineStr">
-        <is>
-          <t>cvc_vknimb_date</t>
-        </is>
-      </c>
+      <c r="N262" s="7" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="inlineStr">

--- a/Сводная_таблица_автоворонок.xlsx
+++ b/Сводная_таблица_автоворонок.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная автоворонки" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сводная автоворонки" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N839"/>
+  <dimension ref="A1:N836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Ютуб Органика, t=19</t>
+          <t>автоворонки, сосуды, СВС, Ютуб Органика, t=19</t>
         </is>
       </c>
       <c r="C32" s="2" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Ютуб Органика, t=15</t>
+          <t>автоворонки, сосуды, СВС, Ютуб Органика, t=15</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб органика, t=19</t>
+          <t>автоворонки, ДБО, Ютуб органика, t=19</t>
         </is>
       </c>
       <c r="C61" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб органика, t=15</t>
+          <t>автоворонки, ДБО, Ютуб органика, t=15</t>
         </is>
       </c>
       <c r="C62" s="2" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>ГП, Ютуб органика, t=19</t>
+          <t>автоворонки, ГП, Ютуб органика, t=19</t>
         </is>
       </c>
       <c r="C89" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>ГП, Ютуб органика, t=15</t>
+          <t>автоворонки, ГП, Ютуб органика, t=15</t>
         </is>
       </c>
       <c r="C90" s="2" t="n"/>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб Реклама, НИМБ, t=19</t>
+          <t>автоворонки, ДБО, Ютуб Реклама, НИМБ, t=19</t>
         </is>
       </c>
       <c r="C117" s="2" t="n"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб Реклама, НИМБ, t=15</t>
+          <t>автоворонки, ДБО, Ютуб Реклама, НИМБ, t=15</t>
         </is>
       </c>
       <c r="C118" s="2" t="n"/>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новый ленд, t=19</t>
+          <t>автоворонки, тег: БОО, Яндекс Реклама новый ленд, t=19</t>
         </is>
       </c>
       <c r="C145" s="2" t="n"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новый ленд, t=15</t>
+          <t>автоворонки, тег: БОО, Яндекс Реклама новый ленд, t=15</t>
         </is>
       </c>
       <c r="C146" s="2" t="n"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама новый ленд, t=19</t>
+          <t>автоворонки, ДБО, Яндекс Реклама новый ленд, t=19</t>
         </is>
       </c>
       <c r="C173" s="2" t="n"/>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама новый ленд, t=15</t>
+          <t>автоворонки, ДБО, Яндекс Реклама новый ленд, t=15</t>
         </is>
       </c>
       <c r="C174" s="2" t="n"/>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, Яндекс Реклама новый ленд, t=19</t>
+          <t>автоворонки, ЖКТ, Яндекс Реклама новый ленд, t=19</t>
         </is>
       </c>
       <c r="C201" s="2" t="n"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, Яндекс Реклама новый ленд, t=15</t>
+          <t>автоворонки, ЖКТ, Яндекс Реклама новый ленд, t=15</t>
         </is>
       </c>
       <c r="C202" s="2" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=19</t>
+          <t>автоворонки, ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=19</t>
         </is>
       </c>
       <c r="C225" s="2" t="n"/>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=15</t>
+          <t>автоворонки, ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=15</t>
         </is>
       </c>
       <c r="C226" s="2" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=19</t>
+          <t>автоворонки, сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=19</t>
         </is>
       </c>
       <c r="C249" s="2" t="n"/>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=15</t>
+          <t>автоворонки, сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=15</t>
         </is>
       </c>
       <c r="C250" s="2" t="n"/>
@@ -8902,7 +8902,11 @@
 cvc_rsya_date = #{current_date}</t>
         </is>
       </c>
-      <c r="N262" s="7" t="inlineStr"/>
+      <c r="N262" s="7" t="inlineStr">
+        <is>
+          <t>cvc_vknimb_date</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
@@ -9383,7 +9387,7 @@
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=19</t>
+          <t>автоворонки, ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=19</t>
         </is>
       </c>
       <c r="C277" s="2" t="n"/>
@@ -9407,7 +9411,7 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=15</t>
+          <t>автоворонки, ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=15</t>
         </is>
       </c>
       <c r="C278" s="2" t="n"/>
@@ -10277,7 +10281,7 @@
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR ВК, t=19</t>
+          <t>автоворонки, ЖКТ, ВК NR, ВК NR ВК, t=19</t>
         </is>
       </c>
       <c r="C305" s="2" t="n"/>
@@ -10301,7 +10305,7 @@
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR ВК, t=15</t>
+          <t>автоворонки, ЖКТ, ВК NR, ВК NR ВК, t=15</t>
         </is>
       </c>
       <c r="C306" s="2" t="n"/>
@@ -11023,7 +11027,7 @@
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, IS NR, t=19</t>
+          <t>автоворонки, ЖКТ, ВК NR, IS NR, t=19</t>
         </is>
       </c>
       <c r="C329" s="2" t="n"/>
@@ -11047,7 +11051,7 @@
       </c>
       <c r="B330" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, IS NR, t=15</t>
+          <t>автоворонки, ЖКТ, ВК NR, IS NR, t=15</t>
         </is>
       </c>
       <c r="C330" s="2" t="n"/>
@@ -11769,7 +11773,7 @@
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR МП, t=19</t>
+          <t>автоворонки, ЖКТ, ВК NR, ВК NR МП, t=19</t>
         </is>
       </c>
       <c r="C353" s="2" t="n"/>
@@ -11793,7 +11797,7 @@
       </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR МП, t=15</t>
+          <t>автоворонки, ЖКТ, ВК NR, ВК NR МП, t=15</t>
         </is>
       </c>
       <c r="C354" s="2" t="n"/>
@@ -12515,7 +12519,7 @@
       </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=19</t>
+          <t>автоворонки, ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=19</t>
         </is>
       </c>
       <c r="C377" s="2" t="n"/>
@@ -12539,7 +12543,7 @@
       </c>
       <c r="B378" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=15</t>
+          <t>автоворонки, ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=15</t>
         </is>
       </c>
       <c r="C378" s="2" t="n"/>
@@ -12924,7 +12928,11 @@
 contr_id = "nr"</t>
         </is>
       </c>
-      <c r="N390" s="7" t="inlineStr"/>
+      <c r="N390" s="7" t="inlineStr">
+        <is>
+          <t>dbo_nrmp_date</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
@@ -13413,7 +13421,7 @@
       </c>
       <c r="B405" s="5" t="inlineStr">
         <is>
-          <t>Яндекс Холодный квиз CHO, БОО, t=19</t>
+          <t>автоворонки, Яндекс Холодный квиз CHO, БОО, t=19</t>
         </is>
       </c>
       <c r="C405" s="2" t="n"/>
@@ -14299,7 +14307,7 @@
       </c>
       <c r="B432" s="5" t="inlineStr">
         <is>
-          <t>ДБО, МАКС, FAQ, t=19</t>
+          <t>автоворонки, ДБО, МАКС, FAQ, t=19</t>
         </is>
       </c>
       <c r="C432" s="2" t="n"/>
@@ -14323,7 +14331,7 @@
       </c>
       <c r="B433" s="5" t="inlineStr">
         <is>
-          <t>ДБО, МАКС, FAQ, t=15</t>
+          <t>автоворонки, ДБО, МАКС, FAQ, t=15</t>
         </is>
       </c>
       <c r="C433" s="2" t="n"/>
@@ -15201,7 +15209,7 @@
       </c>
       <c r="B460" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК, ВК HT, t=19</t>
+          <t>автоворонки, ДБО, ВК, ВК HT, t=19</t>
         </is>
       </c>
       <c r="C460" s="2" t="n"/>
@@ -15225,7 +15233,7 @@
       </c>
       <c r="B461" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК, ВК HT, t=15</t>
+          <t>автоворонки, ДБО, ВК, ВК HT, t=15</t>
         </is>
       </c>
       <c r="C461" s="2" t="n"/>
@@ -16095,7 +16103,7 @@
       </c>
       <c r="B488" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, ВК новая цена, t=19</t>
+          <t>автоворонки, тег: БОО, ВК новая цена, t=19</t>
         </is>
       </c>
       <c r="C488" s="2" t="n"/>
@@ -16119,7 +16127,7 @@
       </c>
       <c r="B489" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, ВК новая цена, t=15</t>
+          <t>автоворонки, тег: БОО, ВК новая цена, t=15</t>
         </is>
       </c>
       <c r="C489" s="2" t="n"/>
@@ -16507,7 +16515,8 @@
       <c r="M501" s="7" t="inlineStr">
         <is>
           <t>condition: boo-vkns19
-choose_time = 19</t>
+choose_time = 19
+boo_ht_date = #{current_date}</t>
         </is>
       </c>
       <c r="N501" s="7" t="inlineStr">
@@ -16760,7 +16769,8 @@
       <c r="M506" s="10" t="inlineStr">
         <is>
           <t>condition: boo-vkns15
-choose_time = 15</t>
+choose_time = 15
+boo_ht_date = #{current_date}</t>
         </is>
       </c>
       <c r="N506" s="8" t="n"/>
@@ -17013,7 +17023,7 @@
       </c>
       <c r="B515" s="5" t="inlineStr">
         <is>
-          <t>Яндекс Холодный квиз CHO, БОО, t=19</t>
+          <t>автоворонки, Яндекс Холодный квиз CHO, БОО, t=19</t>
         </is>
       </c>
       <c r="C515" s="2" t="n"/>
@@ -17899,7 +17909,7 @@
       </c>
       <c r="B542" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Яндекс Реклама, t=19</t>
+          <t>автоворонки, сосуды, СВС, Яндекс Реклама, t=19</t>
         </is>
       </c>
       <c r="C542" s="2" t="n"/>
@@ -17923,7 +17933,7 @@
       </c>
       <c r="B543" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС , Яндекс Реклама, t=15</t>
+          <t>автоворонки, сосуды, СВС , Яндекс Реклама, t=15</t>
         </is>
       </c>
       <c r="C543" s="2" t="n"/>
@@ -18821,7 +18831,7 @@
       </c>
       <c r="B571" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новая цена, t=19</t>
+          <t>автоворонки, тег: БОО, Яндекс Реклама новая цена, t=19</t>
         </is>
       </c>
       <c r="C571" s="2" t="n"/>
@@ -18845,7 +18855,7 @@
       </c>
       <c r="B572" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новая цена, t=15</t>
+          <t>автоворонки, тег: БОО, Яндекс Реклама новая цена, t=15</t>
         </is>
       </c>
       <c r="C572" s="2" t="n"/>
@@ -19795,7 +19805,7 @@
       </c>
       <c r="B600" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама, t=19</t>
+          <t>автоворонки, ДБО, Яндекс Реклама, t=19</t>
         </is>
       </c>
       <c r="C600" s="2" t="n"/>
@@ -19819,7 +19829,7 @@
       </c>
       <c r="B601" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама, t=15</t>
+          <t>автоворонки, ДБО, Яндекс Реклама, t=15</t>
         </is>
       </c>
       <c r="C601" s="2" t="n"/>
@@ -20725,7 +20735,7 @@
       </c>
       <c r="B629" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Ретаргет, t=19</t>
+          <t>автоворонки, тег: БОО, Яндекс Ретаргет, t=19</t>
         </is>
       </c>
       <c r="C629" s="2" t="n"/>
@@ -20749,7 +20759,7 @@
       </c>
       <c r="B630" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Ретаргет, t=15</t>
+          <t>автоворонки, тег: БОО, Яндекс Ретаргет, t=15</t>
         </is>
       </c>
       <c r="C630" s="2" t="n"/>
@@ -21627,7 +21637,7 @@
       </c>
       <c r="B657" s="5" t="inlineStr">
         <is>
-          <t>СВС, сосуды, Яндекс Ретаргет, t=19</t>
+          <t>автоворонки, СВС, сосуды, Яндекс Ретаргет, t=19</t>
         </is>
       </c>
       <c r="C657" s="2" t="n"/>
@@ -21651,7 +21661,7 @@
       </c>
       <c r="B658" s="5" t="inlineStr">
         <is>
-          <t>СВС, сосуды, Яндекс Ретаргет, t=15</t>
+          <t>автоворонки, СВС, сосуды, Яндекс Ретаргет, t=15</t>
         </is>
       </c>
       <c r="C658" s="2" t="n"/>
@@ -22517,7 +22527,7 @@
       </c>
       <c r="B685" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Ретаргет, t=19</t>
+          <t>автоворонки, ДБО, Яндекс Ретаргет, t=19</t>
         </is>
       </c>
       <c r="C685" s="2" t="n"/>
@@ -22541,7 +22551,7 @@
       </c>
       <c r="B686" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Ретаргет, t=15</t>
+          <t>автоворонки, ДБО, Яндекс Ретаргет, t=15</t>
         </is>
       </c>
       <c r="C686" s="2" t="n"/>
@@ -23389,7 +23399,7 @@
       </c>
       <c r="B712" s="5" t="inlineStr">
         <is>
-          <t>БОО, перелив с СПБ</t>
+          <t>автоворонки, БОО, перелив с СПБ</t>
         </is>
       </c>
       <c r="C712" s="2" t="n"/>
@@ -23413,7 +23423,7 @@
       </c>
       <c r="B713" s="5" t="inlineStr">
         <is>
-          <t>БОО, перелив с СПБ</t>
+          <t>автоворонки, БОО, перелив с СПБ</t>
         </is>
       </c>
       <c r="C713" s="2" t="n"/>
@@ -24247,7 +24257,7 @@
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>СПБ, Перелив с БОО</t>
+          <t>автоворонки, СПБ, Перелив с БОО</t>
         </is>
       </c>
       <c r="C738" s="2" t="n"/>
@@ -24271,7 +24281,7 @@
       </c>
       <c r="B739" s="5" t="inlineStr">
         <is>
-          <t>СПБ, Перелив с БОО</t>
+          <t>автоворонки, СПБ, Перелив с БОО</t>
         </is>
       </c>
       <c r="C739" s="2" t="n"/>
@@ -25112,12 +25122,12 @@
     <row r="765">
       <c r="A765" s="4" t="inlineStr">
         <is>
-          <t>Вариант:</t>
+          <t>Тег 19:00:</t>
         </is>
       </c>
       <c r="B765" s="5" t="inlineStr">
         <is>
-          <t>Яндекс Реклама квиз</t>
+          <t>автоворонки, Яндекс Холодный квиз РД, БОО</t>
         </is>
       </c>
       <c r="C765" s="2" t="n"/>
@@ -25136,7 +25146,7 @@
     <row r="766">
       <c r="A766" s="4" t="inlineStr">
         <is>
-          <t>Тег 19:00:</t>
+          <t>Тег 15:00:</t>
         </is>
       </c>
       <c r="B766" s="5" t="inlineStr">
@@ -25160,7 +25170,7 @@
     <row r="767">
       <c r="A767" s="4" t="inlineStr">
         <is>
-          <t>Тег 15:00:</t>
+          <t>Теги регистрации:</t>
         </is>
       </c>
       <c r="B767" s="5" t="inlineStr">
@@ -25184,12 +25194,12 @@
     <row r="768">
       <c r="A768" s="4" t="inlineStr">
         <is>
-          <t>Теги регистрации:</t>
+          <t>Посадочная:</t>
         </is>
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, Яндекс Холодный квиз РД, БОО</t>
+          <t>http://lp.ksamata.ru/boo-kvrd</t>
         </is>
       </c>
       <c r="C768" s="2" t="n"/>
@@ -25208,12 +25218,12 @@
     <row r="769">
       <c r="A769" s="4" t="inlineStr">
         <is>
-          <t>Посадочная:</t>
+          <t>Дата старта:</t>
         </is>
       </c>
       <c r="B769" s="5" t="inlineStr">
         <is>
-          <t>http://lp.ksamata.ru/boo-kvrd</t>
+          <t>01.08.2022</t>
         </is>
       </c>
       <c r="C769" s="2" t="n"/>
@@ -25232,12 +25242,12 @@
     <row r="770">
       <c r="A770" s="4" t="inlineStr">
         <is>
-          <t>Дата старта:</t>
+          <t>Дашборд продаж:</t>
         </is>
       </c>
       <c r="B770" s="5" t="inlineStr">
         <is>
-          <t>01.08.2022</t>
+          <t>https://gc.ksamata.ru/pl/logic/funnel/dashboard?id=134037#pk=alltime</t>
         </is>
       </c>
       <c r="C770" s="2" t="n"/>
@@ -25256,12 +25266,12 @@
     <row r="771">
       <c r="A771" s="4" t="inlineStr">
         <is>
-          <t>Дашборд продаж:</t>
+          <t>Предсписок:</t>
         </is>
       </c>
       <c r="B771" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/logic/funnel/dashboard?id=134037#pk=alltime</t>
+          <t>Нет предсписка</t>
         </is>
       </c>
       <c r="C771" s="2" t="n"/>
@@ -25280,12 +25290,12 @@
     <row r="772">
       <c r="A772" s="4" t="inlineStr">
         <is>
-          <t>Предсписок:</t>
+          <t>Реги общ ГК:</t>
         </is>
       </c>
       <c r="B772" s="5" t="inlineStr">
         <is>
-          <t>Нет предсписка</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C772" s="2" t="n"/>
@@ -25304,12 +25314,12 @@
     <row r="773">
       <c r="A773" s="4" t="inlineStr">
         <is>
-          <t>Реги общ ГК:</t>
+          <t>Реги на 15:00:</t>
         </is>
       </c>
       <c r="B773" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+17%3A00%22%5D%7D%2C%22valueMode%22%3A2%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C773" s="2" t="n"/>
@@ -25328,12 +25338,12 @@
     <row r="774">
       <c r="A774" s="4" t="inlineStr">
         <is>
-          <t>Реги на 15:00:</t>
+          <t>Реги на 19:00:</t>
         </is>
       </c>
       <c r="B774" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+17%3A00%22%5D%7D%2C%22valueMode%22%3A2%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+20%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C774" s="2" t="n"/>
@@ -25352,12 +25362,12 @@
     <row r="775">
       <c r="A775" s="4" t="inlineStr">
         <is>
-          <t>Реги на 19:00:</t>
+          <t>Реги без выбора:</t>
         </is>
       </c>
       <c r="B775" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+20%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A-1%2C%22fieldId%22%3Anull%2C%22fieldValue%22%3Anull%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C775" s="2" t="n"/>
@@ -25374,100 +25384,133 @@
       <c r="N775" s="3" t="n"/>
     </row>
     <row r="776">
-      <c r="A776" s="4" t="inlineStr">
-        <is>
-          <t>Реги без выбора:</t>
-        </is>
-      </c>
-      <c r="B776" s="5" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A-1%2C%22fieldId%22%3Anull%2C%22fieldValue%22%3Anull%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3790589%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
-        </is>
-      </c>
-      <c r="C776" s="2" t="n"/>
-      <c r="D776" s="2" t="n"/>
-      <c r="E776" s="2" t="n"/>
-      <c r="F776" s="2" t="n"/>
-      <c r="G776" s="2" t="n"/>
-      <c r="H776" s="2" t="n"/>
-      <c r="I776" s="2" t="n"/>
-      <c r="J776" s="2" t="n"/>
-      <c r="K776" s="2" t="n"/>
-      <c r="L776" s="2" t="n"/>
-      <c r="M776" s="2" t="n"/>
-      <c r="N776" s="3" t="n"/>
+      <c r="A776" s="6" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B776" s="6" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="C776" s="6" t="inlineStr">
+        <is>
+          <t>Комната GC (аналит.)</t>
+        </is>
+      </c>
+      <c r="D776" s="6" t="inlineStr">
+        <is>
+          <t>Комната Web (вебинар)</t>
+        </is>
+      </c>
+      <c r="E776" s="6" t="inlineStr">
+        <is>
+          <t>Длительность</t>
+        </is>
+      </c>
+      <c r="F776" s="6" t="inlineStr">
+        <is>
+          <t>Повтор</t>
+        </is>
+      </c>
+      <c r="G776" s="6" t="inlineStr">
+        <is>
+          <t>Продажная</t>
+        </is>
+      </c>
+      <c r="H776" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="I776" s="6" t="inlineStr">
+        <is>
+          <t>Тарифы ГК</t>
+        </is>
+      </c>
+      <c r="J776" s="6" t="inlineStr">
+        <is>
+          <t>OTO</t>
+        </is>
+      </c>
+      <c r="K776" s="6" t="inlineStr">
+        <is>
+          <t>Бонусы / Программа</t>
+        </is>
+      </c>
+      <c r="L776" s="6" t="inlineStr">
+        <is>
+          <t>GetCourse / Salebot</t>
+        </is>
+      </c>
+      <c r="M776" s="6" t="inlineStr">
+        <is>
+          <t>Condition / Калькулятор</t>
+        </is>
+      </c>
+      <c r="N776" s="6" t="inlineStr">
+        <is>
+          <t>BotHelp condition</t>
+        </is>
+      </c>
     </row>
     <row r="777">
-      <c r="A777" s="6" t="inlineStr">
-        <is>
-          <t>Время</t>
-        </is>
-      </c>
-      <c r="B777" s="6" t="inlineStr">
-        <is>
-          <t>День</t>
-        </is>
-      </c>
-      <c r="C777" s="6" t="inlineStr">
-        <is>
-          <t>Комната GC (аналит.)</t>
-        </is>
-      </c>
-      <c r="D777" s="6" t="inlineStr">
-        <is>
-          <t>Комната Web (вебинар)</t>
-        </is>
-      </c>
-      <c r="E777" s="6" t="inlineStr">
-        <is>
-          <t>Длительность</t>
-        </is>
-      </c>
-      <c r="F777" s="6" t="inlineStr">
-        <is>
-          <t>Повтор</t>
-        </is>
-      </c>
-      <c r="G777" s="6" t="inlineStr">
-        <is>
-          <t>Продажная</t>
-        </is>
-      </c>
-      <c r="H777" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="I777" s="6" t="inlineStr">
-        <is>
-          <t>Тарифы ГК</t>
-        </is>
-      </c>
-      <c r="J777" s="6" t="inlineStr">
-        <is>
-          <t>OTO</t>
-        </is>
-      </c>
-      <c r="K777" s="6" t="inlineStr">
-        <is>
-          <t>Бонусы / Программа</t>
-        </is>
-      </c>
-      <c r="L777" s="6" t="inlineStr">
-        <is>
-          <t>GetCourse / Salebot</t>
-        </is>
-      </c>
-      <c r="M777" s="6" t="inlineStr">
-        <is>
-          <t>Condition / Калькулятор</t>
-        </is>
-      </c>
-      <c r="N777" s="6" t="inlineStr">
-        <is>
-          <t>BotHelp condition</t>
-        </is>
-      </c>
+      <c r="A777" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B777" s="7" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C777" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/boo1-kvspb</t>
+        </is>
+      </c>
+      <c r="D777" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/boo1-kvspb</t>
+        </is>
+      </c>
+      <c r="E777" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 47м</t>
+        </is>
+      </c>
+      <c r="F777" s="7" t="inlineStr"/>
+      <c r="G777" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dtx/tarif-1spbkv</t>
+        </is>
+      </c>
+      <c r="H777" s="7" t="inlineStr"/>
+      <c r="I777" s="7" t="inlineStr"/>
+      <c r="J777" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dtx/qh_imm_dbbkv</t>
+        </is>
+      </c>
+      <c r="K777" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/boo/bonus_1</t>
+        </is>
+      </c>
+      <c r="L777" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1777415</t>
+        </is>
+      </c>
+      <c r="M777" s="7" t="inlineStr">
+        <is>
+          <t>condition: boo-kvspb19
+boo-kvspb_date = #{current_date}</t>
+        </is>
+      </c>
+      <c r="N777" s="7" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" s="7" t="inlineStr">
@@ -25477,54 +25520,49 @@
       </c>
       <c r="B778" s="7" t="inlineStr">
         <is>
-          <t>1 день</t>
+          <t>2 день</t>
         </is>
       </c>
       <c r="C778" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/boo1-kvspb</t>
+          <t>https://gc.ksamata.ru/boo2-kvspb</t>
         </is>
       </c>
       <c r="D778" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/boo1-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/boo2-kvspb</t>
         </is>
       </c>
       <c r="E778" s="7" t="inlineStr">
         <is>
-          <t>⏱ 1ч 47м</t>
+          <t>⏱ 3ч 3м</t>
         </is>
       </c>
       <c r="F778" s="7" t="inlineStr"/>
       <c r="G778" s="7" t="inlineStr">
         <is>
-          <t>https://t.ksamata.ru/dtx/tarif-1spbkv</t>
-        </is>
-      </c>
-      <c r="H778" s="7" t="inlineStr"/>
+          <t>https://t.ksamata.ru/dtx/tarif-2spbkv</t>
+        </is>
+      </c>
+      <c r="H778" s="7" t="inlineStr">
+        <is>
+          <t>дожим в ГК по куп больш курс</t>
+        </is>
+      </c>
       <c r="I778" s="7" t="inlineStr"/>
-      <c r="J778" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dtx/qh_imm_dbbkv</t>
-        </is>
-      </c>
+      <c r="J778" s="7" t="inlineStr"/>
       <c r="K778" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/boo/bonus_1</t>
+          <t>https://gc.ksamata.ru/boo/bonus_2</t>
         </is>
       </c>
       <c r="L778" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1777415</t>
-        </is>
-      </c>
-      <c r="M778" s="7" t="inlineStr">
-        <is>
-          <t>condition: boo-kvspb19
-boo-kvspb_date = #{current_date}</t>
-        </is>
-      </c>
-      <c r="N778" s="7" t="inlineStr"/>
+          <t>https://salebot.pro/projects/98250/messages?sheet_id=210182</t>
+        </is>
+      </c>
+      <c r="M778" s="8" t="n"/>
+      <c r="N778" s="8" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="7" t="inlineStr">
@@ -25534,47 +25572,39 @@
       </c>
       <c r="B779" s="7" t="inlineStr">
         <is>
-          <t>2 день</t>
+          <t>3 день</t>
         </is>
       </c>
       <c r="C779" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/boo2-kvspb</t>
+          <t>https://gc.ksamata.ru/boo3-kvspb</t>
         </is>
       </c>
       <c r="D779" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/boo2-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/boo3-kvspb</t>
         </is>
       </c>
       <c r="E779" s="7" t="inlineStr">
         <is>
-          <t>⏱ 3ч 3м</t>
+          <t>⏱ 2ч 57м</t>
         </is>
       </c>
       <c r="F779" s="7" t="inlineStr"/>
       <c r="G779" s="7" t="inlineStr">
         <is>
-          <t>https://t.ksamata.ru/dtx/tarif-2spbkv</t>
+          <t>https://t.ksamata.ru/dtx/tarif-2spbzkv</t>
         </is>
       </c>
       <c r="H779" s="7" t="inlineStr">
         <is>
-          <t>дожим в ГК по куп больш курс</t>
+          <t>тарифы с записью</t>
         </is>
       </c>
       <c r="I779" s="7" t="inlineStr"/>
       <c r="J779" s="7" t="inlineStr"/>
-      <c r="K779" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/boo/bonus_2</t>
-        </is>
-      </c>
-      <c r="L779" s="7" t="inlineStr">
-        <is>
-          <t>https://salebot.pro/projects/98250/messages?sheet_id=210182</t>
-        </is>
-      </c>
+      <c r="K779" s="7" t="inlineStr"/>
+      <c r="L779" s="7" t="inlineStr"/>
       <c r="M779" s="8" t="n"/>
       <c r="N779" s="8" t="n"/>
     </row>
@@ -25586,35 +25616,31 @@
       </c>
       <c r="B780" s="7" t="inlineStr">
         <is>
-          <t>3 день</t>
+          <t>4 день</t>
         </is>
       </c>
       <c r="C780" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/boo3-kvspb</t>
+          <t>https://gc.ksamata.ru/boo4-kvspb</t>
         </is>
       </c>
       <c r="D780" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/boo3-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/boo4-kvspb</t>
         </is>
       </c>
       <c r="E780" s="7" t="inlineStr">
         <is>
-          <t>⏱ 2ч 57м</t>
-        </is>
-      </c>
-      <c r="F780" s="7" t="inlineStr"/>
-      <c r="G780" s="7" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/dtx/tarif-2spbzkv</t>
-        </is>
-      </c>
-      <c r="H780" s="7" t="inlineStr">
-        <is>
-          <t>тарифы с записью</t>
-        </is>
-      </c>
+          <t>⏱ 3ч 1м</t>
+        </is>
+      </c>
+      <c r="F780" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/boo4r-kvspb</t>
+        </is>
+      </c>
+      <c r="G780" s="7" t="inlineStr"/>
+      <c r="H780" s="7" t="inlineStr"/>
       <c r="I780" s="7" t="inlineStr"/>
       <c r="J780" s="7" t="inlineStr"/>
       <c r="K780" s="7" t="inlineStr"/>
@@ -25630,27 +25656,27 @@
       </c>
       <c r="B781" s="7" t="inlineStr">
         <is>
-          <t>4 день</t>
+          <t>5 день</t>
         </is>
       </c>
       <c r="C781" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/boo4-kvspb</t>
+          <t>https://gc.ksamata.ru/boo5-kvspb</t>
         </is>
       </c>
       <c r="D781" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/boo4-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/boo5-kvspb</t>
         </is>
       </c>
       <c r="E781" s="7" t="inlineStr">
         <is>
-          <t>⏱ 3ч 1м</t>
+          <t>⏱ 2ч 52м</t>
         </is>
       </c>
       <c r="F781" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/boo4r-kvspb</t>
+          <t>https://gc.ksamata.ru/boo5r-kvspb</t>
         </is>
       </c>
       <c r="G781" s="7" t="inlineStr"/>
@@ -25659,47 +25685,60 @@
       <c r="J781" s="7" t="inlineStr"/>
       <c r="K781" s="7" t="inlineStr"/>
       <c r="L781" s="7" t="inlineStr"/>
-      <c r="M781" s="8" t="n"/>
+      <c r="M781" s="9" t="n"/>
       <c r="N781" s="8" t="n"/>
     </row>
     <row r="782">
-      <c r="A782" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B782" s="7" t="inlineStr">
-        <is>
-          <t>5 день</t>
-        </is>
-      </c>
-      <c r="C782" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/boo5-kvspb</t>
-        </is>
-      </c>
-      <c r="D782" s="7" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/boo5-kvspb</t>
-        </is>
-      </c>
-      <c r="E782" s="7" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 52м</t>
-        </is>
-      </c>
-      <c r="F782" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/boo5r-kvspb</t>
-        </is>
-      </c>
-      <c r="G782" s="7" t="inlineStr"/>
-      <c r="H782" s="7" t="inlineStr"/>
-      <c r="I782" s="7" t="inlineStr"/>
-      <c r="J782" s="7" t="inlineStr"/>
-      <c r="K782" s="7" t="inlineStr"/>
-      <c r="L782" s="7" t="inlineStr"/>
-      <c r="M782" s="9" t="n"/>
+      <c r="A782" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B782" s="10" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C782" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/1boo-kvspb</t>
+        </is>
+      </c>
+      <c r="D782" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/1boo-kvspb</t>
+        </is>
+      </c>
+      <c r="E782" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 47м</t>
+        </is>
+      </c>
+      <c r="F782" s="10" t="inlineStr"/>
+      <c r="G782" s="10" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dtx/tarif-1spbkv</t>
+        </is>
+      </c>
+      <c r="H782" s="10" t="inlineStr"/>
+      <c r="I782" s="10" t="inlineStr"/>
+      <c r="J782" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dtx/qh_imm_dbbkv</t>
+        </is>
+      </c>
+      <c r="K782" s="10" t="inlineStr"/>
+      <c r="L782" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1777418</t>
+        </is>
+      </c>
+      <c r="M782" s="10" t="inlineStr">
+        <is>
+          <t>condition: boo-kvspb15
+boo-kvspb_date = #{current_date}</t>
+        </is>
+      </c>
       <c r="N782" s="8" t="n"/>
     </row>
     <row r="783">
@@ -25710,49 +25749,40 @@
       </c>
       <c r="B783" s="10" t="inlineStr">
         <is>
-          <t>1 день</t>
+          <t>2 день</t>
         </is>
       </c>
       <c r="C783" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/1boo-kvspb</t>
+          <t>https://gc.ksamata.ru/2boo-kvspb</t>
         </is>
       </c>
       <c r="D783" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/1boo-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/2boo-kvspb</t>
         </is>
       </c>
       <c r="E783" s="10" t="inlineStr">
         <is>
-          <t>⏱ 1ч 47м</t>
+          <t>⏱ 3ч 3м</t>
         </is>
       </c>
       <c r="F783" s="10" t="inlineStr"/>
       <c r="G783" s="10" t="inlineStr">
         <is>
-          <t>https://t.ksamata.ru/dtx/tarif-1spbkv</t>
+          <t>https://t.ksamata.ru/dtx/tarif-2spbkv</t>
         </is>
       </c>
       <c r="H783" s="10" t="inlineStr"/>
       <c r="I783" s="10" t="inlineStr"/>
-      <c r="J783" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dtx/qh_imm_dbbkv</t>
-        </is>
-      </c>
+      <c r="J783" s="10" t="inlineStr"/>
       <c r="K783" s="10" t="inlineStr"/>
       <c r="L783" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1777418</t>
-        </is>
-      </c>
-      <c r="M783" s="10" t="inlineStr">
-        <is>
-          <t>condition: boo-kvspb15
-boo-kvspb_date = #{current_date}</t>
-        </is>
-      </c>
+          <t>https://salebot.pro/projects/98250/messages?sheet_id=210186</t>
+        </is>
+      </c>
+      <c r="M783" s="8" t="n"/>
       <c r="N783" s="8" t="n"/>
     </row>
     <row r="784">
@@ -25763,39 +25793,39 @@
       </c>
       <c r="B784" s="10" t="inlineStr">
         <is>
-          <t>2 день</t>
+          <t>3 день</t>
         </is>
       </c>
       <c r="C784" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/2boo-kvspb</t>
+          <t>https://gc.ksamata.ru/3boo-kvspb</t>
         </is>
       </c>
       <c r="D784" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/2boo-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/3boo-kvspb</t>
         </is>
       </c>
       <c r="E784" s="10" t="inlineStr">
         <is>
-          <t>⏱ 3ч 3м</t>
+          <t>⏱ 2ч 57м</t>
         </is>
       </c>
       <c r="F784" s="10" t="inlineStr"/>
       <c r="G784" s="10" t="inlineStr">
         <is>
-          <t>https://t.ksamata.ru/dtx/tarif-2spbkv</t>
-        </is>
-      </c>
-      <c r="H784" s="10" t="inlineStr"/>
+          <t>https://t.ksamata.ru/dtx/tarif-2spbzkv</t>
+        </is>
+      </c>
+      <c r="H784" s="10" t="inlineStr">
+        <is>
+          <t>тарифы с записью</t>
+        </is>
+      </c>
       <c r="I784" s="10" t="inlineStr"/>
       <c r="J784" s="10" t="inlineStr"/>
       <c r="K784" s="10" t="inlineStr"/>
-      <c r="L784" s="10" t="inlineStr">
-        <is>
-          <t>https://salebot.pro/projects/98250/messages?sheet_id=210186</t>
-        </is>
-      </c>
+      <c r="L784" s="10" t="inlineStr"/>
       <c r="M784" s="8" t="n"/>
       <c r="N784" s="8" t="n"/>
     </row>
@@ -25807,35 +25837,31 @@
       </c>
       <c r="B785" s="10" t="inlineStr">
         <is>
-          <t>3 день</t>
+          <t>4 день</t>
         </is>
       </c>
       <c r="C785" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/3boo-kvspb</t>
+          <t>https://gc.ksamata.ru/4boo-kvspb</t>
         </is>
       </c>
       <c r="D785" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/3boo-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/4boo-kvspb</t>
         </is>
       </c>
       <c r="E785" s="10" t="inlineStr">
         <is>
-          <t>⏱ 2ч 57м</t>
-        </is>
-      </c>
-      <c r="F785" s="10" t="inlineStr"/>
-      <c r="G785" s="10" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/dtx/tarif-2spbzkv</t>
-        </is>
-      </c>
-      <c r="H785" s="10" t="inlineStr">
-        <is>
-          <t>тарифы с записью</t>
-        </is>
-      </c>
+          <t>⏱ 3ч 1м</t>
+        </is>
+      </c>
+      <c r="F785" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/4rboo-kvspb</t>
+        </is>
+      </c>
+      <c r="G785" s="10" t="inlineStr"/>
+      <c r="H785" s="10" t="inlineStr"/>
       <c r="I785" s="10" t="inlineStr"/>
       <c r="J785" s="10" t="inlineStr"/>
       <c r="K785" s="10" t="inlineStr"/>
@@ -25851,27 +25877,27 @@
       </c>
       <c r="B786" s="10" t="inlineStr">
         <is>
-          <t>4 день</t>
+          <t>5 день</t>
         </is>
       </c>
       <c r="C786" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/4boo-kvspb</t>
+          <t>https://gc.ksamata.ru/5boo-kvspb</t>
         </is>
       </c>
       <c r="D786" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/4boo-kvspb</t>
+          <t>https://web.ksamatacenter.com/room/5boo-kvspb</t>
         </is>
       </c>
       <c r="E786" s="10" t="inlineStr">
         <is>
-          <t>⏱ 3ч 1м</t>
+          <t>⏱ 2ч 52м</t>
         </is>
       </c>
       <c r="F786" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/4rboo-kvspb</t>
+          <t>https://gc.ksamata.ru/5rboo-kvspb</t>
         </is>
       </c>
       <c r="G786" s="10" t="inlineStr"/>
@@ -25880,56 +25906,40 @@
       <c r="J786" s="10" t="inlineStr"/>
       <c r="K786" s="10" t="inlineStr"/>
       <c r="L786" s="10" t="inlineStr"/>
-      <c r="M786" s="8" t="n"/>
-      <c r="N786" s="8" t="n"/>
-    </row>
-    <row r="787">
-      <c r="A787" s="10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B787" s="10" t="inlineStr">
-        <is>
-          <t>5 день</t>
-        </is>
-      </c>
-      <c r="C787" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/5boo-kvspb</t>
-        </is>
-      </c>
-      <c r="D787" s="10" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/5boo-kvspb</t>
-        </is>
-      </c>
-      <c r="E787" s="10" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 52м</t>
-        </is>
-      </c>
-      <c r="F787" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/5rboo-kvspb</t>
-        </is>
-      </c>
-      <c r="G787" s="10" t="inlineStr"/>
-      <c r="H787" s="10" t="inlineStr"/>
-      <c r="I787" s="10" t="inlineStr"/>
-      <c r="J787" s="10" t="inlineStr"/>
-      <c r="K787" s="10" t="inlineStr"/>
-      <c r="L787" s="10" t="inlineStr"/>
-      <c r="M787" s="9" t="n"/>
-      <c r="N787" s="9" t="n"/>
+      <c r="M786" s="9" t="n"/>
+      <c r="N786" s="9" t="n"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="inlineStr">
+        <is>
+          <t>#30  ДБО Яндекс Реклама квиз</t>
+        </is>
+      </c>
+      <c r="B788" s="2" t="n"/>
+      <c r="C788" s="2" t="n"/>
+      <c r="D788" s="2" t="n"/>
+      <c r="E788" s="2" t="n"/>
+      <c r="F788" s="2" t="n"/>
+      <c r="G788" s="2" t="n"/>
+      <c r="H788" s="2" t="n"/>
+      <c r="I788" s="2" t="n"/>
+      <c r="J788" s="2" t="n"/>
+      <c r="K788" s="2" t="n"/>
+      <c r="L788" s="2" t="n"/>
+      <c r="M788" s="2" t="n"/>
+      <c r="N788" s="3" t="n"/>
     </row>
     <row r="789">
-      <c r="A789" s="1" t="inlineStr">
-        <is>
-          <t>#30  ДБО Яндекс Реклама квиз</t>
-        </is>
-      </c>
-      <c r="B789" s="2" t="n"/>
+      <c r="A789" s="4" t="inlineStr">
+        <is>
+          <t>Продукт:</t>
+        </is>
+      </c>
+      <c r="B789" s="5" t="inlineStr">
+        <is>
+          <t>ДБО</t>
+        </is>
+      </c>
       <c r="C789" s="2" t="n"/>
       <c r="D789" s="2" t="n"/>
       <c r="E789" s="2" t="n"/>
@@ -25946,12 +25956,12 @@
     <row r="790">
       <c r="A790" s="4" t="inlineStr">
         <is>
-          <t>Продукт:</t>
+          <t>Подрядчик:</t>
         </is>
       </c>
       <c r="B790" s="5" t="inlineStr">
         <is>
-          <t>ДБО</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="C790" s="2" t="n"/>
@@ -25970,12 +25980,12 @@
     <row r="791">
       <c r="A791" s="4" t="inlineStr">
         <is>
-          <t>Подрядчик:</t>
+          <t>Тег 19:00:</t>
         </is>
       </c>
       <c r="B791" s="5" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox</t>
         </is>
       </c>
       <c r="C791" s="2" t="n"/>
@@ -25994,12 +26004,12 @@
     <row r="792">
       <c r="A792" s="4" t="inlineStr">
         <is>
-          <t>Вариант:</t>
+          <t>Тег 15:00:</t>
         </is>
       </c>
       <c r="B792" s="5" t="inlineStr">
         <is>
-          <t>Яндекс Реклама квиз</t>
+          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox</t>
         </is>
       </c>
       <c r="C792" s="2" t="n"/>
@@ -26018,7 +26028,7 @@
     <row r="793">
       <c r="A793" s="4" t="inlineStr">
         <is>
-          <t>Тег 19:00:</t>
+          <t>Теги регистрации:</t>
         </is>
       </c>
       <c r="B793" s="5" t="inlineStr">
@@ -26042,12 +26052,12 @@
     <row r="794">
       <c r="A794" s="4" t="inlineStr">
         <is>
-          <t>Тег 15:00:</t>
+          <t>Дата старта:</t>
         </is>
       </c>
       <c r="B794" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox</t>
+          <t>01.08.2022</t>
         </is>
       </c>
       <c r="C794" s="2" t="n"/>
@@ -26066,12 +26076,12 @@
     <row r="795">
       <c r="A795" s="4" t="inlineStr">
         <is>
-          <t>Теги регистрации:</t>
+          <t>Дашборд продаж:</t>
         </is>
       </c>
       <c r="B795" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox</t>
+          <t>https://gc.ksamata.ru/pl/logic/funnel/dashboard?id=134037#pk=alltime</t>
         </is>
       </c>
       <c r="C795" s="2" t="n"/>
@@ -26090,12 +26100,12 @@
     <row r="796">
       <c r="A796" s="4" t="inlineStr">
         <is>
-          <t>Дата старта:</t>
+          <t>Предсписок:</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
         <is>
-          <t>01.08.2022</t>
+          <t>Нет предсписка</t>
         </is>
       </c>
       <c r="C796" s="2" t="n"/>
@@ -26114,12 +26124,12 @@
     <row r="797">
       <c r="A797" s="4" t="inlineStr">
         <is>
-          <t>Дашборд продаж:</t>
+          <t>Реги общ ГК:</t>
         </is>
       </c>
       <c r="B797" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/logic/funnel/dashboard?id=134037#pk=alltime</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3A%22NaN%22%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B%223571852%22%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3A%22false%22%7D%2C%22valueMode%22%3A%22NaN%22%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C797" s="2" t="n"/>
@@ -26138,12 +26148,12 @@
     <row r="798">
       <c r="A798" s="4" t="inlineStr">
         <is>
-          <t>Предсписок:</t>
+          <t>Реги на 15:00:</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
         <is>
-          <t>Нет предсписка</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+17%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B%223571852%22%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C798" s="2" t="n"/>
@@ -26162,12 +26172,12 @@
     <row r="799">
       <c r="A799" s="4" t="inlineStr">
         <is>
-          <t>Реги общ ГК:</t>
+          <t>Реги на 19:00:</t>
         </is>
       </c>
       <c r="B799" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3A%22NaN%22%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B%223571852%22%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3A%22false%22%7D%2C%22valueMode%22%3A%22NaN%22%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+20%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B%223571852%22%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C799" s="2" t="n"/>
@@ -26186,12 +26196,12 @@
     <row r="800">
       <c r="A800" s="4" t="inlineStr">
         <is>
-          <t>Реги на 15:00:</t>
+          <t>Реги без выбора:</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+17%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B%223571852%22%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3Anull%2C%22fieldValue%22%3Anull%2C%22valueMode%22%3A-1%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3571852%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C800" s="2" t="n"/>
@@ -26208,124 +26218,185 @@
       <c r="N800" s="3" t="n"/>
     </row>
     <row r="801">
-      <c r="A801" s="4" t="inlineStr">
-        <is>
-          <t>Реги на 19:00:</t>
-        </is>
-      </c>
-      <c r="B801" s="5" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+20%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B%223571852%22%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
-        </is>
-      </c>
-      <c r="C801" s="2" t="n"/>
-      <c r="D801" s="2" t="n"/>
-      <c r="E801" s="2" t="n"/>
-      <c r="F801" s="2" t="n"/>
-      <c r="G801" s="2" t="n"/>
-      <c r="H801" s="2" t="n"/>
-      <c r="I801" s="2" t="n"/>
-      <c r="J801" s="2" t="n"/>
-      <c r="K801" s="2" t="n"/>
-      <c r="L801" s="2" t="n"/>
-      <c r="M801" s="2" t="n"/>
-      <c r="N801" s="3" t="n"/>
+      <c r="A801" s="6" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B801" s="6" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="C801" s="6" t="inlineStr">
+        <is>
+          <t>Комната GC (аналит.)</t>
+        </is>
+      </c>
+      <c r="D801" s="6" t="inlineStr">
+        <is>
+          <t>Комната Web (вебинар)</t>
+        </is>
+      </c>
+      <c r="E801" s="6" t="inlineStr">
+        <is>
+          <t>Длительность</t>
+        </is>
+      </c>
+      <c r="F801" s="6" t="inlineStr">
+        <is>
+          <t>Повтор</t>
+        </is>
+      </c>
+      <c r="G801" s="6" t="inlineStr">
+        <is>
+          <t>Продажная</t>
+        </is>
+      </c>
+      <c r="H801" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="I801" s="6" t="inlineStr">
+        <is>
+          <t>Тарифы ГК</t>
+        </is>
+      </c>
+      <c r="J801" s="6" t="inlineStr">
+        <is>
+          <t>OTO</t>
+        </is>
+      </c>
+      <c r="K801" s="6" t="inlineStr">
+        <is>
+          <t>Бонусы / Программа</t>
+        </is>
+      </c>
+      <c r="L801" s="6" t="inlineStr">
+        <is>
+          <t>GetCourse / Salebot</t>
+        </is>
+      </c>
+      <c r="M801" s="6" t="inlineStr">
+        <is>
+          <t>Condition / Калькулятор</t>
+        </is>
+      </c>
+      <c r="N801" s="6" t="inlineStr">
+        <is>
+          <t>BotHelp condition</t>
+        </is>
+      </c>
     </row>
     <row r="802">
-      <c r="A802" s="4" t="inlineStr">
-        <is>
-          <t>Реги без выбора:</t>
-        </is>
-      </c>
-      <c r="B802" s="5" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3Anull%2C%22fieldValue%22%3Anull%2C%22valueMode%22%3A-1%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3571852%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
-        </is>
-      </c>
-      <c r="C802" s="2" t="n"/>
-      <c r="D802" s="2" t="n"/>
-      <c r="E802" s="2" t="n"/>
-      <c r="F802" s="2" t="n"/>
-      <c r="G802" s="2" t="n"/>
-      <c r="H802" s="2" t="n"/>
-      <c r="I802" s="2" t="n"/>
-      <c r="J802" s="2" t="n"/>
-      <c r="K802" s="2" t="n"/>
-      <c r="L802" s="2" t="n"/>
-      <c r="M802" s="2" t="n"/>
-      <c r="N802" s="3" t="n"/>
+      <c r="A802" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B802" s="7" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C802" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo1-bookv</t>
+        </is>
+      </c>
+      <c r="D802" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dbo1-bookv</t>
+        </is>
+      </c>
+      <c r="E802" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 43м</t>
+        </is>
+      </c>
+      <c r="F802" s="7" t="inlineStr"/>
+      <c r="G802" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dbo/tarif-1bookv</t>
+        </is>
+      </c>
+      <c r="H802" s="7" t="inlineStr"/>
+      <c r="I802" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo/tarif/curator-bookv</t>
+        </is>
+      </c>
+      <c r="J802" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo/br_mdbookv</t>
+        </is>
+      </c>
+      <c r="K802" s="7" t="inlineStr"/>
+      <c r="L802" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1985038</t>
+        </is>
+      </c>
+      <c r="M802" s="7" t="inlineStr">
+        <is>
+          <t>condition: dbo-bookv19
+dbo-bookv_date = #{current_date}</t>
+        </is>
+      </c>
+      <c r="N802" s="7" t="inlineStr"/>
     </row>
     <row r="803">
-      <c r="A803" s="6" t="inlineStr">
-        <is>
-          <t>Время</t>
-        </is>
-      </c>
-      <c r="B803" s="6" t="inlineStr">
-        <is>
-          <t>День</t>
-        </is>
-      </c>
-      <c r="C803" s="6" t="inlineStr">
-        <is>
-          <t>Комната GC (аналит.)</t>
-        </is>
-      </c>
-      <c r="D803" s="6" t="inlineStr">
-        <is>
-          <t>Комната Web (вебинар)</t>
-        </is>
-      </c>
-      <c r="E803" s="6" t="inlineStr">
-        <is>
-          <t>Длительность</t>
-        </is>
-      </c>
-      <c r="F803" s="6" t="inlineStr">
-        <is>
-          <t>Повтор</t>
-        </is>
-      </c>
-      <c r="G803" s="6" t="inlineStr">
-        <is>
-          <t>Продажная</t>
-        </is>
-      </c>
-      <c r="H803" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="I803" s="6" t="inlineStr">
-        <is>
-          <t>Тарифы ГК</t>
-        </is>
-      </c>
-      <c r="J803" s="6" t="inlineStr">
-        <is>
-          <t>OTO</t>
-        </is>
-      </c>
-      <c r="K803" s="6" t="inlineStr">
-        <is>
-          <t>Бонусы / Программа</t>
-        </is>
-      </c>
-      <c r="L803" s="6" t="inlineStr">
-        <is>
-          <t>GetCourse / Salebot</t>
-        </is>
-      </c>
-      <c r="M803" s="6" t="inlineStr">
-        <is>
-          <t>Condition / Калькулятор</t>
-        </is>
-      </c>
-      <c r="N803" s="6" t="inlineStr">
-        <is>
-          <t>BotHelp condition</t>
-        </is>
-      </c>
+      <c r="A803" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B803" s="7" t="inlineStr">
+        <is>
+          <t>2 день</t>
+        </is>
+      </c>
+      <c r="C803" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo2-bookv</t>
+        </is>
+      </c>
+      <c r="D803" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dbo2-bookv</t>
+        </is>
+      </c>
+      <c r="E803" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 31м</t>
+        </is>
+      </c>
+      <c r="F803" s="7" t="inlineStr"/>
+      <c r="G803" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dbo/tarif-zbookv</t>
+        </is>
+      </c>
+      <c r="H803" s="7" t="inlineStr">
+        <is>
+          <t>тарифы с записью 2,3 дня</t>
+        </is>
+      </c>
+      <c r="I803" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo/tarif/max-bookv</t>
+        </is>
+      </c>
+      <c r="J803" s="7" t="inlineStr"/>
+      <c r="K803" s="7" t="inlineStr"/>
+      <c r="L803" s="7" t="inlineStr">
+        <is>
+          <t>https://salebot.pro/projects/98250/messages?sheet_id=276493</t>
+        </is>
+      </c>
+      <c r="M803" s="8" t="n"/>
+      <c r="N803" s="8" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="7" t="inlineStr">
@@ -26335,54 +26406,37 @@
       </c>
       <c r="B804" s="7" t="inlineStr">
         <is>
-          <t>1 день</t>
+          <t>3 день</t>
         </is>
       </c>
       <c r="C804" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/dbo1-bookv</t>
+          <t>https://gc.ksamata.ru/dbo3-bookv</t>
         </is>
       </c>
       <c r="D804" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/dbo1-bookv</t>
+          <t>https://web.ksamatacenter.com/room/dbo3-bookv</t>
         </is>
       </c>
       <c r="E804" s="7" t="inlineStr">
         <is>
-          <t>⏱ 1ч 43м</t>
+          <t>⏱ 2ч 26м</t>
         </is>
       </c>
       <c r="F804" s="7" t="inlineStr"/>
-      <c r="G804" s="7" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/dbo/tarif-1bookv</t>
-        </is>
-      </c>
+      <c r="G804" s="7" t="inlineStr"/>
       <c r="H804" s="7" t="inlineStr"/>
       <c r="I804" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/dbo/tarif/curator-bookv</t>
-        </is>
-      </c>
-      <c r="J804" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo/br_mdbookv</t>
-        </is>
-      </c>
+          <t>https://gc.ksamata.ru/dbo/tarif/max-int-bookv</t>
+        </is>
+      </c>
+      <c r="J804" s="7" t="inlineStr"/>
       <c r="K804" s="7" t="inlineStr"/>
-      <c r="L804" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1985038</t>
-        </is>
-      </c>
-      <c r="M804" s="7" t="inlineStr">
-        <is>
-          <t>condition: dbo-bookv19
-dbo-bookv_date = #{current_date}</t>
-        </is>
-      </c>
-      <c r="N804" s="7" t="inlineStr"/>
+      <c r="L804" s="7" t="inlineStr"/>
+      <c r="M804" s="8" t="n"/>
+      <c r="N804" s="8" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="7" t="inlineStr">
@@ -26392,47 +26446,31 @@
       </c>
       <c r="B805" s="7" t="inlineStr">
         <is>
-          <t>2 день</t>
+          <t>4 день</t>
         </is>
       </c>
       <c r="C805" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/dbo2-bookv</t>
+          <t>https://gc.ksamata.ru/dbo4-bookv</t>
         </is>
       </c>
       <c r="D805" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/dbo2-bookv</t>
+          <t>https://web.ksamatacenter.com/room/dbo4-bookv</t>
         </is>
       </c>
       <c r="E805" s="7" t="inlineStr">
         <is>
-          <t>⏱ 2ч 31м</t>
+          <t>⏱ 2ч 35м</t>
         </is>
       </c>
       <c r="F805" s="7" t="inlineStr"/>
-      <c r="G805" s="7" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/dbo/tarif-zbookv</t>
-        </is>
-      </c>
-      <c r="H805" s="7" t="inlineStr">
-        <is>
-          <t>тарифы с записью 2,3 дня</t>
-        </is>
-      </c>
-      <c r="I805" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo/tarif/max-bookv</t>
-        </is>
-      </c>
+      <c r="G805" s="7" t="inlineStr"/>
+      <c r="H805" s="7" t="inlineStr"/>
+      <c r="I805" s="7" t="inlineStr"/>
       <c r="J805" s="7" t="inlineStr"/>
       <c r="K805" s="7" t="inlineStr"/>
-      <c r="L805" s="7" t="inlineStr">
-        <is>
-          <t>https://salebot.pro/projects/98250/messages?sheet_id=276493</t>
-        </is>
-      </c>
+      <c r="L805" s="7" t="inlineStr"/>
       <c r="M805" s="8" t="n"/>
       <c r="N805" s="8" t="n"/>
     </row>
@@ -26444,108 +26482,141 @@
       </c>
       <c r="B806" s="7" t="inlineStr">
         <is>
-          <t>3 день</t>
+          <t>5 день</t>
         </is>
       </c>
       <c r="C806" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/dbo3-bookv</t>
+          <t>https://gc.ksamata.ru/dbo5-bookv</t>
         </is>
       </c>
       <c r="D806" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/dbo3-bookv</t>
+          <t>https://web.ksamatacenter.com/room/dbo5-bookv</t>
         </is>
       </c>
       <c r="E806" s="7" t="inlineStr">
         <is>
-          <t>⏱ 2ч 26м</t>
+          <t>⏱ 2ч 54м</t>
         </is>
       </c>
       <c r="F806" s="7" t="inlineStr"/>
       <c r="G806" s="7" t="inlineStr"/>
       <c r="H806" s="7" t="inlineStr"/>
-      <c r="I806" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo/tarif/max-int-bookv</t>
-        </is>
-      </c>
+      <c r="I806" s="7" t="inlineStr"/>
       <c r="J806" s="7" t="inlineStr"/>
       <c r="K806" s="7" t="inlineStr"/>
       <c r="L806" s="7" t="inlineStr"/>
-      <c r="M806" s="8" t="n"/>
+      <c r="M806" s="9" t="n"/>
       <c r="N806" s="8" t="n"/>
     </row>
     <row r="807">
-      <c r="A807" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B807" s="7" t="inlineStr">
-        <is>
-          <t>4 день</t>
-        </is>
-      </c>
-      <c r="C807" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo4-bookv</t>
-        </is>
-      </c>
-      <c r="D807" s="7" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/dbo4-bookv</t>
-        </is>
-      </c>
-      <c r="E807" s="7" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 35м</t>
-        </is>
-      </c>
-      <c r="F807" s="7" t="inlineStr"/>
-      <c r="G807" s="7" t="inlineStr"/>
-      <c r="H807" s="7" t="inlineStr"/>
-      <c r="I807" s="7" t="inlineStr"/>
-      <c r="J807" s="7" t="inlineStr"/>
-      <c r="K807" s="7" t="inlineStr"/>
-      <c r="L807" s="7" t="inlineStr"/>
-      <c r="M807" s="8" t="n"/>
+      <c r="A807" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B807" s="10" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C807" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/1dbo-bookv</t>
+        </is>
+      </c>
+      <c r="D807" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/1dbo-bookv</t>
+        </is>
+      </c>
+      <c r="E807" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 43м</t>
+        </is>
+      </c>
+      <c r="F807" s="10" t="inlineStr"/>
+      <c r="G807" s="10" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dbo/tarif-1bookv</t>
+        </is>
+      </c>
+      <c r="H807" s="10" t="inlineStr"/>
+      <c r="I807" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo/tarif/curator-bookv</t>
+        </is>
+      </c>
+      <c r="J807" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo/br_mdbookv</t>
+        </is>
+      </c>
+      <c r="K807" s="10" t="inlineStr"/>
+      <c r="L807" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1985039</t>
+        </is>
+      </c>
+      <c r="M807" s="10" t="inlineStr">
+        <is>
+          <t>condition: dbo-bookv15
+dbo-bookv_date = #{current_date}</t>
+        </is>
+      </c>
       <c r="N807" s="8" t="n"/>
     </row>
     <row r="808">
-      <c r="A808" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B808" s="7" t="inlineStr">
-        <is>
-          <t>5 день</t>
-        </is>
-      </c>
-      <c r="C808" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo5-bookv</t>
-        </is>
-      </c>
-      <c r="D808" s="7" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/dbo5-bookv</t>
-        </is>
-      </c>
-      <c r="E808" s="7" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 54м</t>
-        </is>
-      </c>
-      <c r="F808" s="7" t="inlineStr"/>
-      <c r="G808" s="7" t="inlineStr"/>
-      <c r="H808" s="7" t="inlineStr"/>
-      <c r="I808" s="7" t="inlineStr"/>
-      <c r="J808" s="7" t="inlineStr"/>
-      <c r="K808" s="7" t="inlineStr"/>
-      <c r="L808" s="7" t="inlineStr"/>
-      <c r="M808" s="9" t="n"/>
+      <c r="A808" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B808" s="10" t="inlineStr">
+        <is>
+          <t>2 день</t>
+        </is>
+      </c>
+      <c r="C808" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/2dbo-bookv</t>
+        </is>
+      </c>
+      <c r="D808" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/2dbo-bookv</t>
+        </is>
+      </c>
+      <c r="E808" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 31м</t>
+        </is>
+      </c>
+      <c r="F808" s="10" t="inlineStr"/>
+      <c r="G808" s="10" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dbo/tarif-zbookv</t>
+        </is>
+      </c>
+      <c r="H808" s="10" t="inlineStr">
+        <is>
+          <t>тарифы с записью 2,3 дня</t>
+        </is>
+      </c>
+      <c r="I808" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dbo/tarif/max-bookv</t>
+        </is>
+      </c>
+      <c r="J808" s="10" t="inlineStr"/>
+      <c r="K808" s="10" t="inlineStr"/>
+      <c r="L808" s="10" t="inlineStr">
+        <is>
+          <t>https://salebot.pro/projects/98250/messages?sheet_id=276496</t>
+        </is>
+      </c>
+      <c r="M808" s="8" t="n"/>
       <c r="N808" s="8" t="n"/>
     </row>
     <row r="809">
@@ -26556,53 +26627,36 @@
       </c>
       <c r="B809" s="10" t="inlineStr">
         <is>
-          <t>1 день</t>
+          <t>3 день</t>
         </is>
       </c>
       <c r="C809" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/1dbo-bookv</t>
+          <t>https://gc.ksamata.ru/3dbo-bookv</t>
         </is>
       </c>
       <c r="D809" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/1dbo-bookv</t>
+          <t>https://web.ksamatacenter.com/room/3dbo-bookv</t>
         </is>
       </c>
       <c r="E809" s="10" t="inlineStr">
         <is>
-          <t>⏱ 1ч 43м</t>
+          <t>⏱ 2ч 26м</t>
         </is>
       </c>
       <c r="F809" s="10" t="inlineStr"/>
-      <c r="G809" s="10" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/dbo/tarif-1bookv</t>
-        </is>
-      </c>
+      <c r="G809" s="10" t="inlineStr"/>
       <c r="H809" s="10" t="inlineStr"/>
       <c r="I809" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/dbo/tarif/curator-bookv</t>
-        </is>
-      </c>
-      <c r="J809" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo/br_mdbookv</t>
-        </is>
-      </c>
+          <t>https://gc.ksamata.ru/dbo/tarif/max-int-bookv</t>
+        </is>
+      </c>
+      <c r="J809" s="10" t="inlineStr"/>
       <c r="K809" s="10" t="inlineStr"/>
-      <c r="L809" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1985039</t>
-        </is>
-      </c>
-      <c r="M809" s="10" t="inlineStr">
-        <is>
-          <t>condition: dbo-bookv15
-dbo-bookv_date = #{current_date}</t>
-        </is>
-      </c>
+      <c r="L809" s="10" t="inlineStr"/>
+      <c r="M809" s="8" t="n"/>
       <c r="N809" s="8" t="n"/>
     </row>
     <row r="810">
@@ -26613,47 +26667,31 @@
       </c>
       <c r="B810" s="10" t="inlineStr">
         <is>
-          <t>2 день</t>
+          <t>4 день</t>
         </is>
       </c>
       <c r="C810" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/2dbo-bookv</t>
+          <t>https://gc.ksamata.ru/4dbo-bookv</t>
         </is>
       </c>
       <c r="D810" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/2dbo-bookv</t>
+          <t>https://web.ksamatacenter.com/room/4dbo-bookv</t>
         </is>
       </c>
       <c r="E810" s="10" t="inlineStr">
         <is>
-          <t>⏱ 2ч 31м</t>
+          <t>⏱ 2ч 35м</t>
         </is>
       </c>
       <c r="F810" s="10" t="inlineStr"/>
-      <c r="G810" s="10" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/dbo/tarif-zbookv</t>
-        </is>
-      </c>
-      <c r="H810" s="10" t="inlineStr">
-        <is>
-          <t>тарифы с записью 2,3 дня</t>
-        </is>
-      </c>
-      <c r="I810" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo/tarif/max-bookv</t>
-        </is>
-      </c>
+      <c r="G810" s="10" t="inlineStr"/>
+      <c r="H810" s="10" t="inlineStr"/>
+      <c r="I810" s="10" t="inlineStr"/>
       <c r="J810" s="10" t="inlineStr"/>
       <c r="K810" s="10" t="inlineStr"/>
-      <c r="L810" s="10" t="inlineStr">
-        <is>
-          <t>https://salebot.pro/projects/98250/messages?sheet_id=276496</t>
-        </is>
-      </c>
+      <c r="L810" s="10" t="inlineStr"/>
       <c r="M810" s="8" t="n"/>
       <c r="N810" s="8" t="n"/>
     </row>
@@ -26665,117 +26703,89 @@
       </c>
       <c r="B811" s="10" t="inlineStr">
         <is>
-          <t>3 день</t>
+          <t>5 день</t>
         </is>
       </c>
       <c r="C811" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/3dbo-bookv</t>
+          <t>https://gc.ksamata.ru/5dbo-bookv</t>
         </is>
       </c>
       <c r="D811" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/3dbo-bookv</t>
+          <t>https://web.ksamatacenter.com/room/5dbo-bookv</t>
         </is>
       </c>
       <c r="E811" s="10" t="inlineStr">
         <is>
-          <t>⏱ 2ч 26м</t>
+          <t>⏱ 2ч 54м</t>
         </is>
       </c>
       <c r="F811" s="10" t="inlineStr"/>
       <c r="G811" s="10" t="inlineStr"/>
       <c r="H811" s="10" t="inlineStr"/>
-      <c r="I811" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/dbo/tarif/max-int-bookv</t>
-        </is>
-      </c>
+      <c r="I811" s="10" t="inlineStr"/>
       <c r="J811" s="10" t="inlineStr"/>
       <c r="K811" s="10" t="inlineStr"/>
       <c r="L811" s="10" t="inlineStr"/>
-      <c r="M811" s="8" t="n"/>
-      <c r="N811" s="8" t="n"/>
-    </row>
-    <row r="812">
-      <c r="A812" s="10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B812" s="10" t="inlineStr">
-        <is>
-          <t>4 день</t>
-        </is>
-      </c>
-      <c r="C812" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/4dbo-bookv</t>
-        </is>
-      </c>
-      <c r="D812" s="10" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/4dbo-bookv</t>
-        </is>
-      </c>
-      <c r="E812" s="10" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 35м</t>
-        </is>
-      </c>
-      <c r="F812" s="10" t="inlineStr"/>
-      <c r="G812" s="10" t="inlineStr"/>
-      <c r="H812" s="10" t="inlineStr"/>
-      <c r="I812" s="10" t="inlineStr"/>
-      <c r="J812" s="10" t="inlineStr"/>
-      <c r="K812" s="10" t="inlineStr"/>
-      <c r="L812" s="10" t="inlineStr"/>
-      <c r="M812" s="8" t="n"/>
-      <c r="N812" s="8" t="n"/>
+      <c r="M811" s="9" t="n"/>
+      <c r="N811" s="9" t="n"/>
     </row>
     <row r="813">
-      <c r="A813" s="10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B813" s="10" t="inlineStr">
-        <is>
-          <t>5 день</t>
-        </is>
-      </c>
-      <c r="C813" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/5dbo-bookv</t>
-        </is>
-      </c>
-      <c r="D813" s="10" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/5dbo-bookv</t>
-        </is>
-      </c>
-      <c r="E813" s="10" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 54м</t>
-        </is>
-      </c>
-      <c r="F813" s="10" t="inlineStr"/>
-      <c r="G813" s="10" t="inlineStr"/>
-      <c r="H813" s="10" t="inlineStr"/>
-      <c r="I813" s="10" t="inlineStr"/>
-      <c r="J813" s="10" t="inlineStr"/>
-      <c r="K813" s="10" t="inlineStr"/>
-      <c r="L813" s="10" t="inlineStr"/>
-      <c r="M813" s="9" t="n"/>
-      <c r="N813" s="9" t="n"/>
+      <c r="A813" s="1" t="inlineStr">
+        <is>
+          <t>#31  СВС Яндекс Реклама квиз БОО</t>
+        </is>
+      </c>
+      <c r="B813" s="2" t="n"/>
+      <c r="C813" s="2" t="n"/>
+      <c r="D813" s="2" t="n"/>
+      <c r="E813" s="2" t="n"/>
+      <c r="F813" s="2" t="n"/>
+      <c r="G813" s="2" t="n"/>
+      <c r="H813" s="2" t="n"/>
+      <c r="I813" s="2" t="n"/>
+      <c r="J813" s="2" t="n"/>
+      <c r="K813" s="2" t="n"/>
+      <c r="L813" s="2" t="n"/>
+      <c r="M813" s="2" t="n"/>
+      <c r="N813" s="3" t="n"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="4" t="inlineStr">
+        <is>
+          <t>Продукт:</t>
+        </is>
+      </c>
+      <c r="B814" s="5" t="inlineStr">
+        <is>
+          <t>СВС</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="n"/>
+      <c r="D814" s="2" t="n"/>
+      <c r="E814" s="2" t="n"/>
+      <c r="F814" s="2" t="n"/>
+      <c r="G814" s="2" t="n"/>
+      <c r="H814" s="2" t="n"/>
+      <c r="I814" s="2" t="n"/>
+      <c r="J814" s="2" t="n"/>
+      <c r="K814" s="2" t="n"/>
+      <c r="L814" s="2" t="n"/>
+      <c r="M814" s="2" t="n"/>
+      <c r="N814" s="3" t="n"/>
     </row>
     <row r="815">
-      <c r="A815" s="1" t="inlineStr">
-        <is>
-          <t>#31  СВС Яндекс Реклама квиз БОО</t>
-        </is>
-      </c>
-      <c r="B815" s="2" t="n"/>
+      <c r="A815" s="4" t="inlineStr">
+        <is>
+          <t>Подрядчик:</t>
+        </is>
+      </c>
+      <c r="B815" s="5" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
       <c r="C815" s="2" t="n"/>
       <c r="D815" s="2" t="n"/>
       <c r="E815" s="2" t="n"/>
@@ -26792,12 +26802,12 @@
     <row r="816">
       <c r="A816" s="4" t="inlineStr">
         <is>
-          <t>Продукт:</t>
+          <t>Тег 19:00:</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
         <is>
-          <t>СВС</t>
+          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
         </is>
       </c>
       <c r="C816" s="2" t="n"/>
@@ -26816,12 +26826,12 @@
     <row r="817">
       <c r="A817" s="4" t="inlineStr">
         <is>
-          <t>Подрядчик:</t>
+          <t>Тег 15:00:</t>
         </is>
       </c>
       <c r="B817" s="5" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
         </is>
       </c>
       <c r="C817" s="2" t="n"/>
@@ -26840,12 +26850,12 @@
     <row r="818">
       <c r="A818" s="4" t="inlineStr">
         <is>
-          <t>Вариант:</t>
+          <t>Теги регистрации:</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
         <is>
-          <t>Яндекс Реклама квиз</t>
+          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
         </is>
       </c>
       <c r="C818" s="2" t="n"/>
@@ -26864,12 +26874,12 @@
     <row r="819">
       <c r="A819" s="4" t="inlineStr">
         <is>
-          <t>Тег 19:00:</t>
+          <t>Дата старта:</t>
         </is>
       </c>
       <c r="B819" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
+          <t>01.08.2022</t>
         </is>
       </c>
       <c r="C819" s="2" t="n"/>
@@ -26888,12 +26898,12 @@
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>Тег 15:00:</t>
+          <t>Дашборд продаж:</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
+          <t>https://gc.ksamata.ru/pl/logic/funnel/dashboard?id=134037#pk=alltime</t>
         </is>
       </c>
       <c r="C820" s="2" t="n"/>
@@ -26912,12 +26922,12 @@
     <row r="821">
       <c r="A821" s="4" t="inlineStr">
         <is>
-          <t>Теги регистрации:</t>
+          <t>Предсписок:</t>
         </is>
       </c>
       <c r="B821" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
+          <t>Нет предсписка</t>
         </is>
       </c>
       <c r="C821" s="2" t="n"/>
@@ -26936,12 +26946,12 @@
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>Дата старта:</t>
+          <t>Реги общ ГК:</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
         <is>
-          <t>01.08.2022</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C822" s="2" t="n"/>
@@ -26960,12 +26970,12 @@
     <row r="823">
       <c r="A823" s="4" t="inlineStr">
         <is>
-          <t>Дашборд продаж:</t>
+          <t>Реги на 15:00:</t>
         </is>
       </c>
       <c r="B823" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/logic/funnel/dashboard?id=134037#pk=alltime</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+17%3A00%22%5D%7D%2C%22valueMode%22%3A2%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C823" s="2" t="n"/>
@@ -26984,12 +26994,12 @@
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>Предсписок:</t>
+          <t>Реги на 19:00:</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
         <is>
-          <t>Нет предсписка</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+20%3A00%22%5D%7D%2C%22valueMode%22%3A2%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C824" s="2" t="n"/>
@@ -27008,12 +27018,12 @@
     <row r="825">
       <c r="A825" s="4" t="inlineStr">
         <is>
-          <t>Реги общ ГК:</t>
+          <t>Реги без выбора:</t>
         </is>
       </c>
       <c r="B825" s="5" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3Anull%2C%22fieldValue%22%3Anull%2C%22valueMode%22%3A-1%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
         </is>
       </c>
       <c r="C825" s="2" t="n"/>
@@ -27030,148 +27040,237 @@
       <c r="N825" s="3" t="n"/>
     </row>
     <row r="826">
-      <c r="A826" s="4" t="inlineStr">
-        <is>
-          <t>Реги на 15:00:</t>
-        </is>
-      </c>
-      <c r="B826" s="5" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+17%3A00%22%5D%7D%2C%22valueMode%22%3A2%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
-        </is>
-      </c>
-      <c r="C826" s="2" t="n"/>
-      <c r="D826" s="2" t="n"/>
-      <c r="E826" s="2" t="n"/>
-      <c r="F826" s="2" t="n"/>
-      <c r="G826" s="2" t="n"/>
-      <c r="H826" s="2" t="n"/>
-      <c r="I826" s="2" t="n"/>
-      <c r="J826" s="2" t="n"/>
-      <c r="K826" s="2" t="n"/>
-      <c r="L826" s="2" t="n"/>
-      <c r="M826" s="2" t="n"/>
-      <c r="N826" s="3" t="n"/>
+      <c r="A826" s="6" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B826" s="6" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="C826" s="6" t="inlineStr">
+        <is>
+          <t>Комната GC (аналит.)</t>
+        </is>
+      </c>
+      <c r="D826" s="6" t="inlineStr">
+        <is>
+          <t>Комната Web (вебинар)</t>
+        </is>
+      </c>
+      <c r="E826" s="6" t="inlineStr">
+        <is>
+          <t>Длительность</t>
+        </is>
+      </c>
+      <c r="F826" s="6" t="inlineStr">
+        <is>
+          <t>Повтор</t>
+        </is>
+      </c>
+      <c r="G826" s="6" t="inlineStr">
+        <is>
+          <t>Продажная</t>
+        </is>
+      </c>
+      <c r="H826" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="I826" s="6" t="inlineStr">
+        <is>
+          <t>Тарифы ГК</t>
+        </is>
+      </c>
+      <c r="J826" s="6" t="inlineStr">
+        <is>
+          <t>OTO</t>
+        </is>
+      </c>
+      <c r="K826" s="6" t="inlineStr">
+        <is>
+          <t>Бонусы / Программа</t>
+        </is>
+      </c>
+      <c r="L826" s="6" t="inlineStr">
+        <is>
+          <t>GetCourse / Salebot</t>
+        </is>
+      </c>
+      <c r="M826" s="6" t="inlineStr">
+        <is>
+          <t>Condition / Калькулятор</t>
+        </is>
+      </c>
+      <c r="N826" s="6" t="inlineStr">
+        <is>
+          <t>BotHelp condition</t>
+        </is>
+      </c>
     </row>
     <row r="827">
-      <c r="A827" s="4" t="inlineStr">
-        <is>
-          <t>Реги на 19:00:</t>
-        </is>
-      </c>
-      <c r="B827" s="5" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3A705606%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+20%3A00%22%5D%7D%2C%22valueMode%22%3A2%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
-        </is>
-      </c>
-      <c r="C827" s="2" t="n"/>
-      <c r="D827" s="2" t="n"/>
-      <c r="E827" s="2" t="n"/>
-      <c r="F827" s="2" t="n"/>
-      <c r="G827" s="2" t="n"/>
-      <c r="H827" s="2" t="n"/>
-      <c r="I827" s="2" t="n"/>
-      <c r="J827" s="2" t="n"/>
-      <c r="K827" s="2" t="n"/>
-      <c r="L827" s="2" t="n"/>
-      <c r="M827" s="2" t="n"/>
-      <c r="N827" s="3" t="n"/>
+      <c r="A827" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B827" s="7" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C827" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs1-yakvboo</t>
+        </is>
+      </c>
+      <c r="D827" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/svs1-yakvboo</t>
+        </is>
+      </c>
+      <c r="E827" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 30м</t>
+        </is>
+      </c>
+      <c r="F827" s="7" t="inlineStr"/>
+      <c r="G827" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/svs/tarif-1yakvboo</t>
+        </is>
+      </c>
+      <c r="H827" s="7" t="inlineStr"/>
+      <c r="I827" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/hv/tarif/curator-yakvboo</t>
+        </is>
+      </c>
+      <c r="J827" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs/back-int-wyakvboo</t>
+        </is>
+      </c>
+      <c r="K827" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs/bonus1</t>
+        </is>
+      </c>
+      <c r="L827" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1627566</t>
+        </is>
+      </c>
+      <c r="M827" s="7" t="inlineStr">
+        <is>
+          <t>condition: svs-yakvboo19
+svs-yakvboo_date = #{current_date}</t>
+        </is>
+      </c>
+      <c r="N827" s="7" t="inlineStr"/>
     </row>
     <row r="828">
-      <c r="A828" s="4" t="inlineStr">
-        <is>
-          <t>Реги без выбора:</t>
-        </is>
-      </c>
-      <c r="B828" s="5" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22fieldId%22%3Anull%2C%22fieldValue%22%3Anull%2C%22valueMode%22%3A-1%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22mode%22%3A%22and%22%2C%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3A%22%22%2C%22fromNDays%22%3A%22%22%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3A%22false%22%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B3572180%5D%2C%22selected_tags%22%3A%5B%22%D0%A0%D0%B5%D0%B3%D0%B8%D1%81%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%7D%7D%2C%22countCondition%22%3A%7B%22checker%22%3A%22nlt%22%2C%22numval%22%3A%22%22%7D%7D%7D%5D%7D%2C%22maxSize%22%3A%22%22%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
-        </is>
-      </c>
-      <c r="C828" s="2" t="n"/>
-      <c r="D828" s="2" t="n"/>
-      <c r="E828" s="2" t="n"/>
-      <c r="F828" s="2" t="n"/>
-      <c r="G828" s="2" t="n"/>
-      <c r="H828" s="2" t="n"/>
-      <c r="I828" s="2" t="n"/>
-      <c r="J828" s="2" t="n"/>
-      <c r="K828" s="2" t="n"/>
-      <c r="L828" s="2" t="n"/>
-      <c r="M828" s="2" t="n"/>
-      <c r="N828" s="3" t="n"/>
+      <c r="A828" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B828" s="7" t="inlineStr">
+        <is>
+          <t>2 день</t>
+        </is>
+      </c>
+      <c r="C828" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs2-yakvboo</t>
+        </is>
+      </c>
+      <c r="D828" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/svs2-yakvboo</t>
+        </is>
+      </c>
+      <c r="E828" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 26м</t>
+        </is>
+      </c>
+      <c r="F828" s="7" t="inlineStr"/>
+      <c r="G828" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/svs/tarif-zyakvboo</t>
+        </is>
+      </c>
+      <c r="H828" s="7" t="inlineStr">
+        <is>
+          <t>тарифы с записью ГЛАВНОГО занятия</t>
+        </is>
+      </c>
+      <c r="I828" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/hv/tarif/max-yakvboo</t>
+        </is>
+      </c>
+      <c r="J828" s="7" t="inlineStr"/>
+      <c r="K828" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs/bonus2</t>
+        </is>
+      </c>
+      <c r="L828" s="7" t="inlineStr">
+        <is>
+          <t>https://salebot.pro/projects/98250/messages?sheet_id=171733</t>
+        </is>
+      </c>
+      <c r="M828" s="8" t="n"/>
+      <c r="N828" s="8" t="n"/>
     </row>
     <row r="829">
-      <c r="A829" s="6" t="inlineStr">
-        <is>
-          <t>Время</t>
-        </is>
-      </c>
-      <c r="B829" s="6" t="inlineStr">
-        <is>
-          <t>День</t>
-        </is>
-      </c>
-      <c r="C829" s="6" t="inlineStr">
-        <is>
-          <t>Комната GC (аналит.)</t>
-        </is>
-      </c>
-      <c r="D829" s="6" t="inlineStr">
-        <is>
-          <t>Комната Web (вебинар)</t>
-        </is>
-      </c>
-      <c r="E829" s="6" t="inlineStr">
-        <is>
-          <t>Длительность</t>
-        </is>
-      </c>
-      <c r="F829" s="6" t="inlineStr">
-        <is>
-          <t>Повтор</t>
-        </is>
-      </c>
-      <c r="G829" s="6" t="inlineStr">
-        <is>
-          <t>Продажная</t>
-        </is>
-      </c>
-      <c r="H829" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-      <c r="I829" s="6" t="inlineStr">
-        <is>
-          <t>Тарифы ГК</t>
-        </is>
-      </c>
-      <c r="J829" s="6" t="inlineStr">
-        <is>
-          <t>OTO</t>
-        </is>
-      </c>
-      <c r="K829" s="6" t="inlineStr">
-        <is>
-          <t>Бонусы / Программа</t>
-        </is>
-      </c>
-      <c r="L829" s="6" t="inlineStr">
-        <is>
-          <t>GetCourse / Salebot</t>
-        </is>
-      </c>
-      <c r="M829" s="6" t="inlineStr">
-        <is>
-          <t>Condition / Калькулятор</t>
-        </is>
-      </c>
-      <c r="N829" s="6" t="inlineStr">
-        <is>
-          <t>BotHelp condition</t>
-        </is>
-      </c>
+      <c r="A829" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B829" s="7" t="inlineStr">
+        <is>
+          <t>3 день</t>
+        </is>
+      </c>
+      <c r="C829" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs3-yakvboo</t>
+        </is>
+      </c>
+      <c r="D829" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/svs3-yakvboo</t>
+        </is>
+      </c>
+      <c r="E829" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 35м</t>
+        </is>
+      </c>
+      <c r="F829" s="7" t="inlineStr"/>
+      <c r="G829" s="7" t="inlineStr"/>
+      <c r="H829" s="7" t="inlineStr"/>
+      <c r="I829" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/hv/tarif/max-int-yakvboo</t>
+        </is>
+      </c>
+      <c r="J829" s="7" t="inlineStr"/>
+      <c r="K829" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs/bonus3</t>
+        </is>
+      </c>
+      <c r="L829" s="7" t="inlineStr"/>
+      <c r="M829" s="8" t="n"/>
+      <c r="N829" s="8" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="7" t="inlineStr">
@@ -27181,58 +27280,37 @@
       </c>
       <c r="B830" s="7" t="inlineStr">
         <is>
-          <t>1 день</t>
+          <t>4 день</t>
         </is>
       </c>
       <c r="C830" s="7" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/svs1-yakvboo</t>
+          <t>https://gc.ksamata.ru/svs4-yakvboo</t>
         </is>
       </c>
       <c r="D830" s="7" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/svs1-yakvboo</t>
+          <t>https://web.ksamatacenter.com/room/svs4-yakvboo</t>
         </is>
       </c>
       <c r="E830" s="7" t="inlineStr">
         <is>
-          <t>⏱ 1ч 30м</t>
-        </is>
-      </c>
-      <c r="F830" s="7" t="inlineStr"/>
-      <c r="G830" s="7" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/svs/tarif-1yakvboo</t>
-        </is>
-      </c>
+          <t>⏱ 2ч 33м</t>
+        </is>
+      </c>
+      <c r="F830" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/4rsvs-yakvboo</t>
+        </is>
+      </c>
+      <c r="G830" s="7" t="inlineStr"/>
       <c r="H830" s="7" t="inlineStr"/>
-      <c r="I830" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/hv/tarif/curator-yakvboo</t>
-        </is>
-      </c>
-      <c r="J830" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs/back-int-wyakvboo</t>
-        </is>
-      </c>
-      <c r="K830" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs/bonus1</t>
-        </is>
-      </c>
-      <c r="L830" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1627566</t>
-        </is>
-      </c>
-      <c r="M830" s="7" t="inlineStr">
-        <is>
-          <t>condition: svs-yakvboo19
-svs-yakvboo_date = #{current_date}</t>
-        </is>
-      </c>
-      <c r="N830" s="7" t="inlineStr"/>
+      <c r="I830" s="7" t="inlineStr"/>
+      <c r="J830" s="7" t="inlineStr"/>
+      <c r="K830" s="7" t="inlineStr"/>
+      <c r="L830" s="7" t="inlineStr"/>
+      <c r="M830" s="8" t="n"/>
+      <c r="N830" s="8" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="7" t="inlineStr">
@@ -27242,176 +27320,169 @@
       </c>
       <c r="B831" s="7" t="inlineStr">
         <is>
+          <t>5 день</t>
+        </is>
+      </c>
+      <c r="C831" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/svs5-yakvboo</t>
+        </is>
+      </c>
+      <c r="D831" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/svs5-yakvboo</t>
+        </is>
+      </c>
+      <c r="E831" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 3ч 0м</t>
+        </is>
+      </c>
+      <c r="F831" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/5rsvs-yakvboo</t>
+        </is>
+      </c>
+      <c r="G831" s="7" t="inlineStr"/>
+      <c r="H831" s="7" t="inlineStr"/>
+      <c r="I831" s="7" t="inlineStr"/>
+      <c r="J831" s="7" t="inlineStr"/>
+      <c r="K831" s="7" t="inlineStr"/>
+      <c r="L831" s="7" t="inlineStr"/>
+      <c r="M831" s="9" t="n"/>
+      <c r="N831" s="8" t="n"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B832" s="10" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C832" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/1svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="D832" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/1svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="E832" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 30м</t>
+        </is>
+      </c>
+      <c r="F832" s="10" t="inlineStr"/>
+      <c r="G832" s="10" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/svs/tarif-1yakvboo</t>
+        </is>
+      </c>
+      <c r="H832" s="10" t="inlineStr"/>
+      <c r="I832" s="10" t="inlineStr"/>
+      <c r="J832" s="10" t="inlineStr"/>
+      <c r="K832" s="10" t="inlineStr"/>
+      <c r="L832" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1628657</t>
+        </is>
+      </c>
+      <c r="M832" s="10" t="inlineStr">
+        <is>
+          <t>condition: svs-yakvboo15
+svs-yakvboo_date = #{current_date}</t>
+        </is>
+      </c>
+      <c r="N832" s="8" t="n"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B833" s="10" t="inlineStr">
+        <is>
           <t>2 день</t>
         </is>
       </c>
-      <c r="C831" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs2-yakvboo</t>
-        </is>
-      </c>
-      <c r="D831" s="7" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/svs2-yakvboo</t>
-        </is>
-      </c>
-      <c r="E831" s="7" t="inlineStr">
+      <c r="C833" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/2svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="D833" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/2svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="E833" s="10" t="inlineStr">
         <is>
           <t>⏱ 2ч 26м</t>
         </is>
       </c>
-      <c r="F831" s="7" t="inlineStr"/>
-      <c r="G831" s="7" t="inlineStr">
+      <c r="F833" s="10" t="inlineStr"/>
+      <c r="G833" s="10" t="inlineStr">
         <is>
           <t>https://t.ksamata.ru/svs/tarif-zyakvboo</t>
         </is>
       </c>
-      <c r="H831" s="7" t="inlineStr">
+      <c r="H833" s="10" t="inlineStr">
         <is>
           <t>тарифы с записью ГЛАВНОГО занятия</t>
         </is>
       </c>
-      <c r="I831" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/hv/tarif/max-yakvboo</t>
-        </is>
-      </c>
-      <c r="J831" s="7" t="inlineStr"/>
-      <c r="K831" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs/bonus2</t>
-        </is>
-      </c>
-      <c r="L831" s="7" t="inlineStr">
-        <is>
-          <t>https://salebot.pro/projects/98250/messages?sheet_id=171733</t>
-        </is>
-      </c>
-      <c r="M831" s="8" t="n"/>
-      <c r="N831" s="8" t="n"/>
-    </row>
-    <row r="832">
-      <c r="A832" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B832" s="7" t="inlineStr">
-        <is>
-          <t>3 день</t>
-        </is>
-      </c>
-      <c r="C832" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs3-yakvboo</t>
-        </is>
-      </c>
-      <c r="D832" s="7" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/svs3-yakvboo</t>
-        </is>
-      </c>
-      <c r="E832" s="7" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 35м</t>
-        </is>
-      </c>
-      <c r="F832" s="7" t="inlineStr"/>
-      <c r="G832" s="7" t="inlineStr"/>
-      <c r="H832" s="7" t="inlineStr"/>
-      <c r="I832" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/hv/tarif/max-int-yakvboo</t>
-        </is>
-      </c>
-      <c r="J832" s="7" t="inlineStr"/>
-      <c r="K832" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs/bonus3</t>
-        </is>
-      </c>
-      <c r="L832" s="7" t="inlineStr"/>
-      <c r="M832" s="8" t="n"/>
-      <c r="N832" s="8" t="n"/>
-    </row>
-    <row r="833">
-      <c r="A833" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B833" s="7" t="inlineStr">
-        <is>
-          <t>4 день</t>
-        </is>
-      </c>
-      <c r="C833" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs4-yakvboo</t>
-        </is>
-      </c>
-      <c r="D833" s="7" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/svs4-yakvboo</t>
-        </is>
-      </c>
-      <c r="E833" s="7" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 33м</t>
-        </is>
-      </c>
-      <c r="F833" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/4rsvs-yakvboo</t>
-        </is>
-      </c>
-      <c r="G833" s="7" t="inlineStr"/>
-      <c r="H833" s="7" t="inlineStr"/>
-      <c r="I833" s="7" t="inlineStr"/>
-      <c r="J833" s="7" t="inlineStr"/>
-      <c r="K833" s="7" t="inlineStr"/>
-      <c r="L833" s="7" t="inlineStr"/>
+      <c r="I833" s="10" t="inlineStr"/>
+      <c r="J833" s="10" t="inlineStr"/>
+      <c r="K833" s="10" t="inlineStr"/>
+      <c r="L833" s="10" t="inlineStr">
+        <is>
+          <t>https://salebot.pro/projects/98250/messages?sheet_id=171753</t>
+        </is>
+      </c>
       <c r="M833" s="8" t="n"/>
       <c r="N833" s="8" t="n"/>
     </row>
     <row r="834">
-      <c r="A834" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B834" s="7" t="inlineStr">
-        <is>
-          <t>5 день</t>
-        </is>
-      </c>
-      <c r="C834" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/svs5-yakvboo</t>
-        </is>
-      </c>
-      <c r="D834" s="7" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/svs5-yakvboo</t>
-        </is>
-      </c>
-      <c r="E834" s="7" t="inlineStr">
-        <is>
-          <t>⏱ 3ч 0м</t>
-        </is>
-      </c>
-      <c r="F834" s="7" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/5rsvs-yakvboo</t>
-        </is>
-      </c>
-      <c r="G834" s="7" t="inlineStr"/>
-      <c r="H834" s="7" t="inlineStr"/>
-      <c r="I834" s="7" t="inlineStr"/>
-      <c r="J834" s="7" t="inlineStr"/>
-      <c r="K834" s="7" t="inlineStr"/>
-      <c r="L834" s="7" t="inlineStr"/>
-      <c r="M834" s="9" t="n"/>
+      <c r="A834" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B834" s="10" t="inlineStr">
+        <is>
+          <t>3 день</t>
+        </is>
+      </c>
+      <c r="C834" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/3svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="D834" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/3svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="E834" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 35м</t>
+        </is>
+      </c>
+      <c r="F834" s="10" t="inlineStr"/>
+      <c r="G834" s="10" t="inlineStr"/>
+      <c r="H834" s="10" t="inlineStr"/>
+      <c r="I834" s="10" t="inlineStr"/>
+      <c r="J834" s="10" t="inlineStr"/>
+      <c r="K834" s="10" t="inlineStr"/>
+      <c r="L834" s="10" t="inlineStr"/>
+      <c r="M834" s="8" t="n"/>
       <c r="N834" s="8" t="n"/>
     </row>
     <row r="835">
@@ -27422,45 +27493,36 @@
       </c>
       <c r="B835" s="10" t="inlineStr">
         <is>
-          <t>1 день</t>
+          <t>4 день</t>
         </is>
       </c>
       <c r="C835" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/1svs-yakvboo</t>
+          <t>https://gc.ksamata.ru/4svs-yakvboo</t>
         </is>
       </c>
       <c r="D835" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/1svs-yakvboo</t>
+          <t>https://web.ksamatacenter.com/room/4svs-yakvboo</t>
         </is>
       </c>
       <c r="E835" s="10" t="inlineStr">
         <is>
-          <t>⏱ 1ч 30м</t>
-        </is>
-      </c>
-      <c r="F835" s="10" t="inlineStr"/>
-      <c r="G835" s="10" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/svs/tarif-1yakvboo</t>
-        </is>
-      </c>
+          <t>⏱ 2ч 33м</t>
+        </is>
+      </c>
+      <c r="F835" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/r4svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="G835" s="10" t="inlineStr"/>
       <c r="H835" s="10" t="inlineStr"/>
       <c r="I835" s="10" t="inlineStr"/>
       <c r="J835" s="10" t="inlineStr"/>
       <c r="K835" s="10" t="inlineStr"/>
-      <c r="L835" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=1628657</t>
-        </is>
-      </c>
-      <c r="M835" s="10" t="inlineStr">
-        <is>
-          <t>condition: svs-yakvboo15
-svs-yakvboo_date = #{current_date}</t>
-        </is>
-      </c>
+      <c r="L835" s="10" t="inlineStr"/>
+      <c r="M835" s="8" t="n"/>
       <c r="N835" s="8" t="n"/>
     </row>
     <row r="836">
@@ -27471,164 +27533,40 @@
       </c>
       <c r="B836" s="10" t="inlineStr">
         <is>
-          <t>2 день</t>
+          <t>5 день</t>
         </is>
       </c>
       <c r="C836" s="10" t="inlineStr">
         <is>
-          <t>https://gc.ksamata.ru/2svs-yakvboo</t>
+          <t>https://gc.ksamata.ru/5svs-yakvboo</t>
         </is>
       </c>
       <c r="D836" s="10" t="inlineStr">
         <is>
-          <t>https://web.ksamatacenter.com/room/2svs-yakvboo</t>
+          <t>https://web.ksamatacenter.com/room/5svs-yakvboo</t>
         </is>
       </c>
       <c r="E836" s="10" t="inlineStr">
         <is>
-          <t>⏱ 2ч 26м</t>
-        </is>
-      </c>
-      <c r="F836" s="10" t="inlineStr"/>
-      <c r="G836" s="10" t="inlineStr">
-        <is>
-          <t>https://t.ksamata.ru/svs/tarif-zyakvboo</t>
-        </is>
-      </c>
-      <c r="H836" s="10" t="inlineStr">
-        <is>
-          <t>тарифы с записью ГЛАВНОГО занятия</t>
-        </is>
-      </c>
+          <t>⏱ 3ч 0м</t>
+        </is>
+      </c>
+      <c r="F836" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/r5svs-yakvboo</t>
+        </is>
+      </c>
+      <c r="G836" s="10" t="inlineStr"/>
+      <c r="H836" s="10" t="inlineStr"/>
       <c r="I836" s="10" t="inlineStr"/>
       <c r="J836" s="10" t="inlineStr"/>
       <c r="K836" s="10" t="inlineStr"/>
-      <c r="L836" s="10" t="inlineStr">
-        <is>
-          <t>https://salebot.pro/projects/98250/messages?sheet_id=171753</t>
-        </is>
-      </c>
-      <c r="M836" s="8" t="n"/>
-      <c r="N836" s="8" t="n"/>
-    </row>
-    <row r="837">
-      <c r="A837" s="10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B837" s="10" t="inlineStr">
-        <is>
-          <t>3 день</t>
-        </is>
-      </c>
-      <c r="C837" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/3svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="D837" s="10" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/3svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="E837" s="10" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 35м</t>
-        </is>
-      </c>
-      <c r="F837" s="10" t="inlineStr"/>
-      <c r="G837" s="10" t="inlineStr"/>
-      <c r="H837" s="10" t="inlineStr"/>
-      <c r="I837" s="10" t="inlineStr"/>
-      <c r="J837" s="10" t="inlineStr"/>
-      <c r="K837" s="10" t="inlineStr"/>
-      <c r="L837" s="10" t="inlineStr"/>
-      <c r="M837" s="8" t="n"/>
-      <c r="N837" s="8" t="n"/>
-    </row>
-    <row r="838">
-      <c r="A838" s="10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B838" s="10" t="inlineStr">
-        <is>
-          <t>4 день</t>
-        </is>
-      </c>
-      <c r="C838" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/4svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="D838" s="10" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/4svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="E838" s="10" t="inlineStr">
-        <is>
-          <t>⏱ 2ч 33м</t>
-        </is>
-      </c>
-      <c r="F838" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/r4svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="G838" s="10" t="inlineStr"/>
-      <c r="H838" s="10" t="inlineStr"/>
-      <c r="I838" s="10" t="inlineStr"/>
-      <c r="J838" s="10" t="inlineStr"/>
-      <c r="K838" s="10" t="inlineStr"/>
-      <c r="L838" s="10" t="inlineStr"/>
-      <c r="M838" s="8" t="n"/>
-      <c r="N838" s="8" t="n"/>
-    </row>
-    <row r="839">
-      <c r="A839" s="10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="B839" s="10" t="inlineStr">
-        <is>
-          <t>5 день</t>
-        </is>
-      </c>
-      <c r="C839" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/5svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="D839" s="10" t="inlineStr">
-        <is>
-          <t>https://web.ksamatacenter.com/room/5svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="E839" s="10" t="inlineStr">
-        <is>
-          <t>⏱ 3ч 0м</t>
-        </is>
-      </c>
-      <c r="F839" s="10" t="inlineStr">
-        <is>
-          <t>https://gc.ksamata.ru/r5svs-yakvboo</t>
-        </is>
-      </c>
-      <c r="G839" s="10" t="inlineStr"/>
-      <c r="H839" s="10" t="inlineStr"/>
-      <c r="I839" s="10" t="inlineStr"/>
-      <c r="J839" s="10" t="inlineStr"/>
-      <c r="K839" s="10" t="inlineStr"/>
-      <c r="L839" s="10" t="inlineStr"/>
-      <c r="M839" s="9" t="n"/>
-      <c r="N839" s="9" t="n"/>
+      <c r="L836" s="10" t="inlineStr"/>
+      <c r="M836" s="9" t="n"/>
+      <c r="N836" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="581">
+  <mergeCells count="578">
     <mergeCell ref="B308:N308"/>
     <mergeCell ref="B379:N379"/>
     <mergeCell ref="M158:M162"/>
@@ -27651,7 +27589,6 @@
     <mergeCell ref="M186:M190"/>
     <mergeCell ref="B232:N232"/>
     <mergeCell ref="B150:N150"/>
-    <mergeCell ref="N804:N813"/>
     <mergeCell ref="B326:N326"/>
     <mergeCell ref="B513:N513"/>
     <mergeCell ref="B684:N684"/>
@@ -27669,8 +27606,8 @@
     <mergeCell ref="B87:N87"/>
     <mergeCell ref="B519:N519"/>
     <mergeCell ref="B823:N823"/>
-    <mergeCell ref="N830:N839"/>
     <mergeCell ref="M238:M240"/>
+    <mergeCell ref="B814:N814"/>
     <mergeCell ref="B285:N285"/>
     <mergeCell ref="B64:N64"/>
     <mergeCell ref="M345:M347"/>
@@ -27688,7 +27625,6 @@
     <mergeCell ref="M395:M399"/>
     <mergeCell ref="B743:N743"/>
     <mergeCell ref="B432:N432"/>
-    <mergeCell ref="M830:M834"/>
     <mergeCell ref="B311:N311"/>
     <mergeCell ref="M751:M755"/>
     <mergeCell ref="B382:N382"/>
@@ -27705,10 +27641,10 @@
     <mergeCell ref="B603:N603"/>
     <mergeCell ref="B377:N377"/>
     <mergeCell ref="B29:N29"/>
+    <mergeCell ref="M777:M781"/>
     <mergeCell ref="B329:N329"/>
     <mergeCell ref="B627:N627"/>
     <mergeCell ref="B316:N316"/>
-    <mergeCell ref="M804:M808"/>
     <mergeCell ref="B95:N95"/>
     <mergeCell ref="B89:N89"/>
     <mergeCell ref="B331:N331"/>
@@ -27725,11 +27661,13 @@
     <mergeCell ref="B72:N72"/>
     <mergeCell ref="B90:N90"/>
     <mergeCell ref="B655:N655"/>
+    <mergeCell ref="N802:N811"/>
     <mergeCell ref="B184:N184"/>
     <mergeCell ref="B657:N657"/>
     <mergeCell ref="A141:N141"/>
     <mergeCell ref="B42:N42"/>
     <mergeCell ref="B471:N471"/>
+    <mergeCell ref="M832:M836"/>
     <mergeCell ref="B769:N769"/>
     <mergeCell ref="B148:N148"/>
     <mergeCell ref="B179:N179"/>
@@ -27774,6 +27712,7 @@
     <mergeCell ref="B98:N98"/>
     <mergeCell ref="B225:N225"/>
     <mergeCell ref="B274:N274"/>
+    <mergeCell ref="M827:M831"/>
     <mergeCell ref="M561:M565"/>
     <mergeCell ref="M417:M421"/>
     <mergeCell ref="B461:N461"/>
@@ -27786,7 +27725,6 @@
     <mergeCell ref="N670:N679"/>
     <mergeCell ref="B485:N485"/>
     <mergeCell ref="A169:N169"/>
-    <mergeCell ref="N778:N787"/>
     <mergeCell ref="B251:N251"/>
     <mergeCell ref="B493:N493"/>
     <mergeCell ref="B487:N487"/>
@@ -27849,7 +27787,6 @@
     <mergeCell ref="B430:N430"/>
     <mergeCell ref="B119:N119"/>
     <mergeCell ref="M647:M651"/>
-    <mergeCell ref="M778:M782"/>
     <mergeCell ref="B824:N824"/>
     <mergeCell ref="B69:N69"/>
     <mergeCell ref="B628:N628"/>
@@ -27889,7 +27826,6 @@
     <mergeCell ref="B6:N6"/>
     <mergeCell ref="B204:N204"/>
     <mergeCell ref="B198:N198"/>
-    <mergeCell ref="M809:M813"/>
     <mergeCell ref="B667:N667"/>
     <mergeCell ref="M390:M394"/>
     <mergeCell ref="B356:N356"/>
@@ -27900,6 +27836,7 @@
     <mergeCell ref="M675:M679"/>
     <mergeCell ref="B306:N306"/>
     <mergeCell ref="B719:N719"/>
+    <mergeCell ref="M802:M806"/>
     <mergeCell ref="B433:N433"/>
     <mergeCell ref="B62:N62"/>
     <mergeCell ref="B233:N233"/>
@@ -27910,11 +27847,11 @@
     <mergeCell ref="B435:N435"/>
     <mergeCell ref="B720:N720"/>
     <mergeCell ref="B70:N70"/>
+    <mergeCell ref="A788:N788"/>
     <mergeCell ref="B228:N228"/>
     <mergeCell ref="N642:N651"/>
     <mergeCell ref="N473:N482"/>
     <mergeCell ref="B88:N88"/>
-    <mergeCell ref="A789:N789"/>
     <mergeCell ref="B818:N818"/>
     <mergeCell ref="A28:N28"/>
     <mergeCell ref="B609:N609"/>
@@ -27926,13 +27863,14 @@
     <mergeCell ref="B375:N375"/>
     <mergeCell ref="M670:M674"/>
     <mergeCell ref="B415:N415"/>
+    <mergeCell ref="M807:M811"/>
     <mergeCell ref="B123:N123"/>
     <mergeCell ref="B715:N715"/>
     <mergeCell ref="A484:N484"/>
     <mergeCell ref="B439:N439"/>
     <mergeCell ref="A428:N428"/>
-    <mergeCell ref="B802:N802"/>
     <mergeCell ref="B12:N12"/>
+    <mergeCell ref="B789:N789"/>
     <mergeCell ref="B248:N248"/>
     <mergeCell ref="B441:N441"/>
     <mergeCell ref="B739:N739"/>
@@ -27982,6 +27920,7 @@
     <mergeCell ref="B547:N547"/>
     <mergeCell ref="B495:N495"/>
     <mergeCell ref="M74:M78"/>
+    <mergeCell ref="N827:N836"/>
     <mergeCell ref="B38:N38"/>
     <mergeCell ref="B747:N747"/>
     <mergeCell ref="N74:N83"/>
@@ -28017,10 +27956,10 @@
     <mergeCell ref="B210:N210"/>
     <mergeCell ref="B381:N381"/>
     <mergeCell ref="B552:N552"/>
+    <mergeCell ref="A813:N813"/>
     <mergeCell ref="N290:N299"/>
     <mergeCell ref="B170:N170"/>
     <mergeCell ref="A373:N373"/>
-    <mergeCell ref="A815:N815"/>
     <mergeCell ref="M191:M195"/>
     <mergeCell ref="M262:M266"/>
     <mergeCell ref="B333:N333"/>
@@ -28032,7 +27971,6 @@
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B172:N172"/>
     <mergeCell ref="B234:N234"/>
-    <mergeCell ref="M783:M787"/>
     <mergeCell ref="A735:N735"/>
     <mergeCell ref="B99:N99"/>
     <mergeCell ref="B568:N568"/>
@@ -28053,7 +27991,6 @@
     <mergeCell ref="M642:M646"/>
     <mergeCell ref="B412:N412"/>
     <mergeCell ref="B468:N468"/>
-    <mergeCell ref="M835:M839"/>
     <mergeCell ref="B539:N539"/>
     <mergeCell ref="B710:N710"/>
     <mergeCell ref="B145:N145"/>
@@ -28105,7 +28042,6 @@
     <mergeCell ref="B226:N226"/>
     <mergeCell ref="B364:N364"/>
     <mergeCell ref="B413:N413"/>
-    <mergeCell ref="B776:N776"/>
     <mergeCell ref="B695:N695"/>
     <mergeCell ref="B284:N284"/>
     <mergeCell ref="B222:N222"/>
@@ -28127,6 +28063,7 @@
     <mergeCell ref="B408:N408"/>
     <mergeCell ref="B464:N464"/>
     <mergeCell ref="B579:N579"/>
+    <mergeCell ref="B815:N815"/>
     <mergeCell ref="B116:N116"/>
     <mergeCell ref="M556:M560"/>
     <mergeCell ref="B352:N352"/>
@@ -28137,6 +28074,7 @@
     <mergeCell ref="B410:N410"/>
     <mergeCell ref="B466:N466"/>
     <mergeCell ref="B637:N637"/>
+    <mergeCell ref="N777:N786"/>
     <mergeCell ref="B118:N118"/>
     <mergeCell ref="M729:M733"/>
     <mergeCell ref="M321:M323"/>
@@ -28151,7 +28089,6 @@
     <mergeCell ref="B121:N121"/>
     <mergeCell ref="B357:N357"/>
     <mergeCell ref="B721:N721"/>
-    <mergeCell ref="B826:N826"/>
     <mergeCell ref="B71:N71"/>
     <mergeCell ref="B236:N236"/>
     <mergeCell ref="M241:M243"/>
@@ -28166,9 +28103,9 @@
     <mergeCell ref="B521:N521"/>
     <mergeCell ref="B665:N665"/>
     <mergeCell ref="B736:N736"/>
+    <mergeCell ref="M782:M786"/>
+    <mergeCell ref="B2:N2"/>
     <mergeCell ref="B798:N798"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B828:N828"/>
     <mergeCell ref="M290:M294"/>
     <mergeCell ref="B60:N60"/>
     <mergeCell ref="B231:N231"/>
@@ -28177,7 +28114,6 @@
     <mergeCell ref="B523:N523"/>
     <mergeCell ref="B790:N790"/>
     <mergeCell ref="B765:N765"/>
-    <mergeCell ref="B827:N827"/>
     <mergeCell ref="B569:N569"/>
     <mergeCell ref="M590:M594"/>
     <mergeCell ref="B668:N668"/>
@@ -28193,7 +28129,6 @@
     <mergeCell ref="B411:N411"/>
     <mergeCell ref="B516:N516"/>
     <mergeCell ref="B774:N774"/>
-    <mergeCell ref="B801:N801"/>
     <mergeCell ref="B488:N488"/>
     <mergeCell ref="B282:N282"/>
     <mergeCell ref="B580:N580"/>

--- a/Сводная_таблица_автоворонок.xlsx
+++ b/Сводная_таблица_автоворонок.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N839"/>
+  <dimension ref="A1:N866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Ютуб органика</t>
+          <t>Регистрация, Ютуб органика, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Ютуб Органика, t=19</t>
+          <t>сосуды, СВС, Ютуб Органика, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний, АВ Время: 19</t>
         </is>
       </c>
       <c r="C32" s="2" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Ютуб Органика, t=15</t>
+          <t>сосуды, СВС, Ютуб Органика, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний, АВ Время: 15</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Жизнь(СВС)</t>
+          <t>Регистрация, Жизнь(СВС), АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: СВС, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний</t>
         </is>
       </c>
       <c r="C34" s="2" t="n"/>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб органика, t=19</t>
+          <t>ДБО, Ютуб органика, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний, АВ Время: 19</t>
         </is>
       </c>
       <c r="C61" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб органика, t=15</t>
+          <t>ДБО, Ютуб органика, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний, АВ Время: 15</t>
         </is>
       </c>
       <c r="C62" s="2" t="n"/>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, РД</t>
+          <t>Регистрация, РД, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний</t>
         </is>
       </c>
       <c r="C63" s="2" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>ГП, Ютуб органика, t=19</t>
+          <t>ГП, Ютуб органика, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ГП, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний, АВ Время: 19</t>
         </is>
       </c>
       <c r="C89" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>ГП, Ютуб органика, t=15</t>
+          <t>ГП, Ютуб органика, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ГП, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний, АВ Время: 15</t>
         </is>
       </c>
       <c r="C90" s="2" t="n"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Ютуб органика, Ютуб О, ГП</t>
+          <t>Регистрация, Ютуб органика, Ютуб О, ГП, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ГП, АВ Канал: Ютуб, АВ Направление: Органика, АВ Подрядчик: Внутренний</t>
         </is>
       </c>
       <c r="C91" s="2" t="n"/>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб Реклама, НИМБ, t=19</t>
+          <t>ДБО, Ютуб Реклама, НИМБ, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Ютуб, АВ Направление: Реклама, АВ Подрядчик: НИМБ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C117" s="2" t="n"/>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Ютуб Реклама, НИМБ, t=15</t>
+          <t>ДБО, Ютуб Реклама, НИМБ, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Ютуб, АВ Направление: Реклама, АВ Подрядчик: НИМБ, АВ Время: 15</t>
         </is>
       </c>
       <c r="C118" s="2" t="n"/>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Ютуб Реклама, НИМБ, РД</t>
+          <t>Регистрация, Ютуб Реклама, НИМБ, РД, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: Ютуб, АВ Направление: Реклама, АВ Подрядчик: НИМБ</t>
         </is>
       </c>
       <c r="C119" s="2" t="n"/>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новый ленд, t=19</t>
+          <t>тег: БОО, Яндекс Реклама новый ленд, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C145" s="2" t="n"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новый ленд, t=15</t>
+          <t>тег: БОО, Яндекс Реклама новый ленд, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 15</t>
         </is>
       </c>
       <c r="C146" s="2" t="n"/>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, яндекс, Детокс, РСЯ</t>
+          <t>Регистрация, яндекс, Детокс, РСЯ, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ</t>
         </is>
       </c>
       <c r="C147" s="2" t="n"/>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама новый ленд, t=19</t>
+          <t>ДБО, Яндекс Реклама новый ленд, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C173" s="2" t="n"/>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама новый ленд, t=15</t>
+          <t>ДБО, Яндекс Реклама новый ленд, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 15</t>
         </is>
       </c>
       <c r="C174" s="2" t="n"/>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, РСЯ, РД</t>
+          <t>Регистрация, РСЯ, РД, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ</t>
         </is>
       </c>
       <c r="C175" s="2" t="n"/>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, Яндекс Реклама новый ленд, t=19</t>
+          <t>ЖКТ, Яндекс Реклама новый ленд, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C201" s="2" t="n"/>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, Яндекс Реклама новый ленд, t=15</t>
+          <t>ЖКТ, Яндекс Реклама новый ленд, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 15</t>
         </is>
       </c>
       <c r="C202" s="2" t="n"/>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Реклама новый ленд, ЖКТ, РСЯ</t>
+          <t>Регистрация, Яндекс Реклама новый ленд, ЖКТ, РСЯ, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ЖКТ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ</t>
         </is>
       </c>
       <c r="C203" s="2" t="n"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=19</t>
+          <t>ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЩЖ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C225" s="2" t="n"/>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=15</t>
+          <t>ЩЖ, Яндекс Реклама новый ленд, РСЯ, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЩЖ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 15</t>
         </is>
       </c>
       <c r="C226" s="2" t="n"/>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Реклама новый ленд, ЩЖ, РСЯ</t>
+          <t>Регистрация, Яндекс Реклама новый ленд, ЩЖ, РСЯ, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ЩЖ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ</t>
         </is>
       </c>
       <c r="C227" s="2" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=19</t>
+          <t>сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C249" s="2" t="n"/>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=15</t>
+          <t>сосуды, СВС, Яндекс Реклама новый ленд, РСЯ, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 15</t>
         </is>
       </c>
       <c r="C250" s="2" t="n"/>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, сосуды, РСЯ</t>
+          <t>Регистрация, сосуды, РСЯ, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ</t>
         </is>
       </c>
       <c r="C251" s="2" t="n"/>
@@ -8902,7 +8902,11 @@
 cvc_rsya_date = #{current_date}</t>
         </is>
       </c>
-      <c r="N262" s="7" t="inlineStr"/>
+      <c r="N262" s="7" t="inlineStr">
+        <is>
+          <t>cvc_vknimb_date</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
@@ -9383,7 +9387,7 @@
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=19</t>
+          <t>ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: In Stream, АВ Подрядчик: NR, АВ Время: 19</t>
         </is>
       </c>
       <c r="C277" s="2" t="n"/>
@@ -9407,7 +9411,7 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=15</t>
+          <t>ДБО, ВК NR, ВК NR ВК, ВК NR IS, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: In Stream, АВ Подрядчик: NR, АВ Время: 15</t>
         </is>
       </c>
       <c r="C278" s="2" t="n"/>
@@ -9431,7 +9435,7 @@
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, ВК Сода, РД, ВК NR ВК, ВК NR IS, ВК NR</t>
+          <t>Регистрация, ВК Сода, РД, ВК NR ВК, ВК NR IS, ВК NR, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: In Stream, АВ Подрядчик: NR</t>
         </is>
       </c>
       <c r="C279" s="2" t="n"/>
@@ -10277,7 +10281,7 @@
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR ВК, t=19</t>
+          <t>ЖКТ, ВК NR, ВК NR ВК, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: NR, АВ Время: 19</t>
         </is>
       </c>
       <c r="C305" s="2" t="n"/>
@@ -10301,7 +10305,7 @@
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR ВК, t=15</t>
+          <t>ЖКТ, ВК NR, ВК NR ВК, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: NR, АВ Время: 15</t>
         </is>
       </c>
       <c r="C306" s="2" t="n"/>
@@ -10325,7 +10329,7 @@
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, ЖКТ, ВК NR ВК, ВК NR</t>
+          <t>Регистрация, ЖКТ, ВК NR ВК, ВК NR, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: NR</t>
         </is>
       </c>
       <c r="C307" s="2" t="n"/>
@@ -11023,7 +11027,7 @@
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, IS NR, t=19</t>
+          <t>ЖКТ, ВК NR, IS NR, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: In Stream, АВ Подрядчик: NR, АВ Время: 19</t>
         </is>
       </c>
       <c r="C329" s="2" t="n"/>
@@ -11047,7 +11051,7 @@
       </c>
       <c r="B330" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, IS NR, t=15</t>
+          <t>ЖКТ, ВК NR, IS NR, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: In Stream, АВ Подрядчик: NR, АВ Время: 15</t>
         </is>
       </c>
       <c r="C330" s="2" t="n"/>
@@ -11071,7 +11075,7 @@
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, ЖКТ, ВК NR IS, ВК NR</t>
+          <t>Регистрация, ЖКТ, ВК NR IS, ВК NR, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: In Stream, АВ Подрядчик: NR</t>
         </is>
       </c>
       <c r="C331" s="2" t="n"/>
@@ -11769,7 +11773,7 @@
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR МП, t=19</t>
+          <t>ЖКТ, ВК NR, ВК NR МП, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: Маркетплатформа, АВ Подрядчик: NR, АВ Время: 19</t>
         </is>
       </c>
       <c r="C353" s="2" t="n"/>
@@ -11793,7 +11797,7 @@
       </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
-          <t>ЖКТ, ВК NR, ВК NR МП, t=15</t>
+          <t>ЖКТ, ВК NR, ВК NR МП, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: Маркетплатформа, АВ Подрядчик: NR, АВ Время: 15</t>
         </is>
       </c>
       <c r="C354" s="2" t="n"/>
@@ -11817,7 +11821,7 @@
       </c>
       <c r="B355" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, ЖКТ, ВК NR МП, ВК NR</t>
+          <t>Регистрация, ЖКТ, ВК NR МП, ВК NR, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ЖКТ, АВ Канал: ВК, АВ Направление: Маркетплатформа, АВ Подрядчик: NR</t>
         </is>
       </c>
       <c r="C355" s="2" t="n"/>
@@ -12515,7 +12519,7 @@
       </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=19</t>
+          <t>ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: Маркетплатформа, АВ Подрядчик: NR, АВ Время: 19</t>
         </is>
       </c>
       <c r="C377" s="2" t="n"/>
@@ -12539,7 +12543,7 @@
       </c>
       <c r="B378" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=15</t>
+          <t>ДБО, ВК NR, ВК NR ВК, ВК NR МП, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: Маркетплатформа, АВ Подрядчик: NR, АВ Время: 15</t>
         </is>
       </c>
       <c r="C378" s="2" t="n"/>
@@ -12563,7 +12567,7 @@
       </c>
       <c r="B379" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, РД, ВК NR МП, ВК NR ВК, ВК NR</t>
+          <t>Регистрация, РД, ВК NR МП, ВК NR ВК, ВК NR, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: Маркетплатформа, АВ Подрядчик: NR</t>
         </is>
       </c>
       <c r="C379" s="2" t="n"/>
@@ -12924,7 +12928,11 @@
 contr_id = "nr"</t>
         </is>
       </c>
-      <c r="N390" s="7" t="inlineStr"/>
+      <c r="N390" s="7" t="inlineStr">
+        <is>
+          <t>dbo_nrmp_date</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
@@ -13413,7 +13421,7 @@
       </c>
       <c r="B405" s="5" t="inlineStr">
         <is>
-          <t>Яндекс Холодный квиз CHO, БОО, t=19</t>
+          <t>Яндекс Холодный квиз CHO, БОО, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: ИНХАУЗ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C405" s="2" t="n"/>
@@ -13437,7 +13445,7 @@
       </c>
       <c r="B406" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Детокс, ВК БАИНГ, ВК</t>
+          <t>Регистрация, Детокс, ВК БАИНГ, ВК, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: ИНХАУЗ</t>
         </is>
       </c>
       <c r="C406" s="2" t="n"/>
@@ -14299,7 +14307,7 @@
       </c>
       <c r="B432" s="5" t="inlineStr">
         <is>
-          <t>ДБО, МАКС, FAQ, t=19</t>
+          <t>ДБО, МАКС, FAQ, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: МАКС, АВ Направление: Посевы, АВ Подрядчик: NR, АВ Время: 19</t>
         </is>
       </c>
       <c r="C432" s="2" t="n"/>
@@ -14323,7 +14331,7 @@
       </c>
       <c r="B433" s="5" t="inlineStr">
         <is>
-          <t>ДБО, МАКС, FAQ, t=15</t>
+          <t>ДБО, МАКС, FAQ, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: МАКС, АВ Направление: Посевы, АВ Подрядчик: NR, АВ Время: 15</t>
         </is>
       </c>
       <c r="C433" s="2" t="n"/>
@@ -14347,7 +14355,7 @@
       </c>
       <c r="B434" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, МАКС, РД, FAQ</t>
+          <t>Регистрация, МАКС, РД, FAQ, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: МАКС, АВ Направление: Посевы, АВ Подрядчик: NR</t>
         </is>
       </c>
       <c r="C434" s="2" t="n"/>
@@ -15201,7 +15209,7 @@
       </c>
       <c r="B460" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК, ВК HT, t=19</t>
+          <t>ДБО, ВК, ВК HT, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: HT, АВ Время: 19</t>
         </is>
       </c>
       <c r="C460" s="2" t="n"/>
@@ -15225,7 +15233,7 @@
       </c>
       <c r="B461" s="5" t="inlineStr">
         <is>
-          <t>ДБО, ВК, ВК HT, t=15</t>
+          <t>ДБО, ВК, ВК HT, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: HT, АВ Время: 15</t>
         </is>
       </c>
       <c r="C461" s="2" t="n"/>
@@ -15249,7 +15257,7 @@
       </c>
       <c r="B462" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, РД, ВК HT, ВК</t>
+          <t>Регистрация, РД, ВК HT, ВК, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: HT</t>
         </is>
       </c>
       <c r="C462" s="2" t="n"/>
@@ -15605,7 +15613,7 @@
       <c r="M473" s="7" t="inlineStr">
         <is>
           <t>condition: dbo-ht-19
-dbo-date = #{current_date}
+dbo_ht_date = #{current_date}
 ct_av = 19
 contr_id = "ht"</t>
         </is>
@@ -15828,7 +15836,7 @@
       <c r="M478" s="10" t="inlineStr">
         <is>
           <t>condition: dbo-ht-15
-dbo-date = #{current_date}
+dbo_ht_date = #{current_date}
 ct_av = 15
 contr_id = "ht"</t>
         </is>
@@ -16095,7 +16103,7 @@
       </c>
       <c r="B488" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, ВК новая цена, t=19</t>
+          <t>тег: БОО, ВК новая цена, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: HT, АВ Время: 19</t>
         </is>
       </c>
       <c r="C488" s="2" t="n"/>
@@ -16119,7 +16127,7 @@
       </c>
       <c r="B489" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, ВК новая цена, t=15</t>
+          <t>тег: БОО, ВК новая цена, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: HT, АВ Время: 15</t>
         </is>
       </c>
       <c r="C489" s="2" t="n"/>
@@ -16143,7 +16151,7 @@
       </c>
       <c r="B490" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Детокс, ВК HT</t>
+          <t>Регистрация, Детокс, ВК HT, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: HT</t>
         </is>
       </c>
       <c r="C490" s="2" t="n"/>
@@ -16507,7 +16515,8 @@
       <c r="M501" s="7" t="inlineStr">
         <is>
           <t>condition: boo-vkns19
-choose_time = 19</t>
+choose_time = 19
+boo_ht_date = #{current_date}</t>
         </is>
       </c>
       <c r="N501" s="7" t="inlineStr">
@@ -16760,7 +16769,8 @@
       <c r="M506" s="10" t="inlineStr">
         <is>
           <t>condition: boo-vkns15
-choose_time = 15</t>
+choose_time = 15
+boo_ht_date = #{current_date}</t>
         </is>
       </c>
       <c r="N506" s="8" t="n"/>
@@ -17013,7 +17023,7 @@
       </c>
       <c r="B515" s="5" t="inlineStr">
         <is>
-          <t>Яндекс Холодный квиз CHO, БОО, t=19</t>
+          <t>Яндекс Холодный квиз CHO, БОО, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: ИНХАУЗ, АВ Время: 19</t>
         </is>
       </c>
       <c r="C515" s="2" t="n"/>
@@ -17037,7 +17047,7 @@
       </c>
       <c r="B516" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Детокс, ВК БАИНГ, ВК</t>
+          <t>Регистрация, Детокс, ВК БАИНГ, ВК, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: ВК, АВ Направление: Реклама, АВ Подрядчик: ИНХАУЗ</t>
         </is>
       </c>
       <c r="C516" s="2" t="n"/>
@@ -17899,7 +17909,7 @@
       </c>
       <c r="B542" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС, Яндекс Реклама, t=19</t>
+          <t>сосуды, СВС, Яндекс Реклама, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C542" s="2" t="n"/>
@@ -17923,7 +17933,7 @@
       </c>
       <c r="B543" s="5" t="inlineStr">
         <is>
-          <t>сосуды, СВС , Яндекс Реклама, t=15</t>
+          <t>сосуды, СВС, Яндекс Реклама, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C543" s="2" t="n"/>
@@ -17947,7 +17957,7 @@
       </c>
       <c r="B544" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Реклама, Жизнь(СВС)</t>
+          <t>Регистрация, Яндекс Реклама, Жизнь(СВС), АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C544" s="2" t="n"/>
@@ -18821,7 +18831,7 @@
       </c>
       <c r="B571" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новая цена, t=19</t>
+          <t>тег: БОО, Яндекс Реклама новая цена, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C571" s="2" t="n"/>
@@ -18845,7 +18855,7 @@
       </c>
       <c r="B572" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Реклама новая цена, t=15</t>
+          <t>тег: БОО, Яндекс Реклама новая цена, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C572" s="2" t="n"/>
@@ -18869,7 +18879,7 @@
       </c>
       <c r="B573" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Реклама, яндекс, Детокс</t>
+          <t>Регистрация, Яндекс Реклама, яндекс, Детокс, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C573" s="2" t="n"/>
@@ -19795,7 +19805,7 @@
       </c>
       <c r="B600" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама, t=19</t>
+          <t>ДБО, Яндекс Реклама, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C600" s="2" t="n"/>
@@ -19819,7 +19829,7 @@
       </c>
       <c r="B601" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Реклама, t=15</t>
+          <t>ДБО, Яндекс Реклама, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C601" s="2" t="n"/>
@@ -19843,7 +19853,7 @@
       </c>
       <c r="B602" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Реклама, РД</t>
+          <t>Регистрация, Яндекс Реклама, РД, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Реклама, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C602" s="2" t="n"/>
@@ -20725,7 +20735,7 @@
       </c>
       <c r="B629" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Ретаргет, t=19</t>
+          <t>тег: БОО, Яндекс Ретаргет, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C629" s="2" t="n"/>
@@ -20749,7 +20759,7 @@
       </c>
       <c r="B630" s="5" t="inlineStr">
         <is>
-          <t>тег: БОО, Яндекс Ретаргет, t=15</t>
+          <t>тег: БОО, Яндекс Ретаргет, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C630" s="2" t="n"/>
@@ -20773,7 +20783,7 @@
       </c>
       <c r="B631" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Реклама, яндекс, Детокс</t>
+          <t>Регистрация, Яндекс Реклама, яндекс, Детокс, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C631" s="2" t="n"/>
@@ -21627,7 +21637,7 @@
       </c>
       <c r="B657" s="5" t="inlineStr">
         <is>
-          <t>СВС, сосуды, Яндекс Ретаргет, t=19</t>
+          <t>СВС, сосуды, Яндекс Ретаргет, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C657" s="2" t="n"/>
@@ -21651,7 +21661,7 @@
       </c>
       <c r="B658" s="5" t="inlineStr">
         <is>
-          <t>СВС, сосуды, Яндекс Ретаргет, t=15</t>
+          <t>СВС, сосуды, Яндекс Ретаргет, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C658" s="2" t="n"/>
@@ -21675,7 +21685,7 @@
       </c>
       <c r="B659" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Ретаргет, Жизнь(СВС)</t>
+          <t>Регистрация, Яндекс Ретаргет, Жизнь(СВС), АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C659" s="2" t="n"/>
@@ -22517,7 +22527,7 @@
       </c>
       <c r="B685" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Ретаргет, t=19</t>
+          <t>ДБО, Яндекс Ретаргет, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C685" s="2" t="n"/>
@@ -22541,7 +22551,7 @@
       </c>
       <c r="B686" s="5" t="inlineStr">
         <is>
-          <t>ДБО, Яндекс Ретаргет, t=15</t>
+          <t>ДБО, Яндекс Ретаргет, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C686" s="2" t="n"/>
@@ -22565,7 +22575,7 @@
       </c>
       <c r="B687" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Яндекс Ретаргет, РД, яндекс</t>
+          <t>Регистрация, Яндекс Ретаргет, РД, яндекс, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Ретаргет, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C687" s="2" t="n"/>
@@ -23389,7 +23399,7 @@
       </c>
       <c r="B712" s="5" t="inlineStr">
         <is>
-          <t>БОО, перелив с СПБ</t>
+          <t>БОО, перелив с СПБ, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Перелив, АВ Направление: Перелив с БОО, АВ Подрядчик: Внутренний, АВ Время: 19</t>
         </is>
       </c>
       <c r="C712" s="2" t="n"/>
@@ -23413,7 +23423,7 @@
       </c>
       <c r="B713" s="5" t="inlineStr">
         <is>
-          <t>БОО, перелив с СПБ</t>
+          <t>БОО, перелив с СПБ, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Перелив, АВ Направление: Перелив с БОО, АВ Подрядчик: Внутренний, АВ Время: 15</t>
         </is>
       </c>
       <c r="C713" s="2" t="n"/>
@@ -23437,7 +23447,7 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, Детокс, перелив</t>
+          <t>Регистрация, Детокс, перелив, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: Перелив, АВ Направление: Перелив с БОО, АВ Подрядчик: Внутренний</t>
         </is>
       </c>
       <c r="C714" s="2" t="n"/>
@@ -24247,7 +24257,7 @@
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>СПБ, Перелив с БОО</t>
+          <t>СПБ, Перелив с БОО, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Перелив, АВ Направление: Перелив с ДБО, АВ Подрядчик: Внутренний, АВ Время: 19</t>
         </is>
       </c>
       <c r="C738" s="2" t="n"/>
@@ -24271,7 +24281,7 @@
       </c>
       <c r="B739" s="5" t="inlineStr">
         <is>
-          <t>СПБ, Перелив с БОО</t>
+          <t>СПБ, Перелив с БОО, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Перелив, АВ Направление: Перелив с ДБО, АВ Подрядчик: Внутренний, АВ Время: 15</t>
         </is>
       </c>
       <c r="C739" s="2" t="n"/>
@@ -24295,7 +24305,7 @@
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Регистрация, ДБО, перелив</t>
+          <t>Регистрация, ДБО, перелив, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: Перелив, АВ Направление: Перелив с ДБО, АВ Подрядчик: Внутренний</t>
         </is>
       </c>
       <c r="C740" s="2" t="n"/>
@@ -25141,7 +25151,7 @@
       </c>
       <c r="B766" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, Яндекс Холодный квиз РД, БОО</t>
+          <t>автоворонки, Яндекс Холодный квиз РД, БОО, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C766" s="2" t="n"/>
@@ -25165,7 +25175,7 @@
       </c>
       <c r="B767" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, Яндекс Холодный квиз РД, БОО</t>
+          <t>автоворонки, Яндекс Холодный квиз РД, БОО, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C767" s="2" t="n"/>
@@ -25189,7 +25199,7 @@
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, Яндекс Холодный квиз РД, БОО</t>
+          <t>автоворонки, Яндекс Холодный квиз РД, БОО, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: БОО, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C768" s="2" t="n"/>
@@ -26023,7 +26033,7 @@
       </c>
       <c r="B793" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox</t>
+          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C793" s="2" t="n"/>
@@ -26047,7 +26057,7 @@
       </c>
       <c r="B794" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox</t>
+          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C794" s="2" t="n"/>
@@ -26071,7 +26081,7 @@
       </c>
       <c r="B795" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox</t>
+          <t>автоворонки, СПБ, Яндекс Холодный квиз Detox, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДБО, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C795" s="2" t="n"/>
@@ -26869,7 +26879,7 @@
       </c>
       <c r="B819" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
+          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей, АВ Время: 19</t>
         </is>
       </c>
       <c r="C819" s="2" t="n"/>
@@ -26893,7 +26903,7 @@
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
+          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей, АВ Время: 15</t>
         </is>
       </c>
       <c r="C820" s="2" t="n"/>
@@ -26917,7 +26927,7 @@
       </c>
       <c r="B821" s="5" t="inlineStr">
         <is>
-          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс</t>
+          <t>автоворонки, СВС, Яндекс Реклама квиз Детокс, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: СВС, АВ Канал: Яндекс, АВ Направление: Квиз, АВ Подрядчик: Алексей</t>
         </is>
       </c>
       <c r="C821" s="2" t="n"/>
@@ -27627,8 +27637,876 @@
       <c r="M839" s="9" t="n"/>
       <c r="N839" s="9" t="n"/>
     </row>
+    <row r="841">
+      <c r="A841" s="1" t="inlineStr">
+        <is>
+          <t>#32  ДЫХАНИЕ НИМБ РСЯ</t>
+        </is>
+      </c>
+      <c r="B841" s="2" t="n"/>
+      <c r="C841" s="2" t="n"/>
+      <c r="D841" s="2" t="n"/>
+      <c r="E841" s="2" t="n"/>
+      <c r="F841" s="2" t="n"/>
+      <c r="G841" s="2" t="n"/>
+      <c r="H841" s="2" t="n"/>
+      <c r="I841" s="2" t="n"/>
+      <c r="J841" s="2" t="n"/>
+      <c r="K841" s="2" t="n"/>
+      <c r="L841" s="2" t="n"/>
+      <c r="M841" s="2" t="n"/>
+      <c r="N841" s="3" t="n"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="4" t="inlineStr">
+        <is>
+          <t>Продукт:</t>
+        </is>
+      </c>
+      <c r="B842" s="5" t="inlineStr">
+        <is>
+          <t>ДЫХАНИЕ</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="n"/>
+      <c r="D842" s="2" t="n"/>
+      <c r="E842" s="2" t="n"/>
+      <c r="F842" s="2" t="n"/>
+      <c r="G842" s="2" t="n"/>
+      <c r="H842" s="2" t="n"/>
+      <c r="I842" s="2" t="n"/>
+      <c r="J842" s="2" t="n"/>
+      <c r="K842" s="2" t="n"/>
+      <c r="L842" s="2" t="n"/>
+      <c r="M842" s="2" t="n"/>
+      <c r="N842" s="3" t="n"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="4" t="inlineStr">
+        <is>
+          <t>Подрядчик:</t>
+        </is>
+      </c>
+      <c r="B843" s="5" t="inlineStr">
+        <is>
+          <t>НИМБ</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="n"/>
+      <c r="D843" s="2" t="n"/>
+      <c r="E843" s="2" t="n"/>
+      <c r="F843" s="2" t="n"/>
+      <c r="G843" s="2" t="n"/>
+      <c r="H843" s="2" t="n"/>
+      <c r="I843" s="2" t="n"/>
+      <c r="J843" s="2" t="n"/>
+      <c r="K843" s="2" t="n"/>
+      <c r="L843" s="2" t="n"/>
+      <c r="M843" s="2" t="n"/>
+      <c r="N843" s="3" t="n"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="4" t="inlineStr">
+        <is>
+          <t>Вариант:</t>
+        </is>
+      </c>
+      <c r="B844" s="5" t="inlineStr">
+        <is>
+          <t>РСЯ</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="n"/>
+      <c r="D844" s="2" t="n"/>
+      <c r="E844" s="2" t="n"/>
+      <c r="F844" s="2" t="n"/>
+      <c r="G844" s="2" t="n"/>
+      <c r="H844" s="2" t="n"/>
+      <c r="I844" s="2" t="n"/>
+      <c r="J844" s="2" t="n"/>
+      <c r="K844" s="2" t="n"/>
+      <c r="L844" s="2" t="n"/>
+      <c r="M844" s="2" t="n"/>
+      <c r="N844" s="3" t="n"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="4" t="inlineStr">
+        <is>
+          <t>Тег 19:00:</t>
+        </is>
+      </c>
+      <c r="B845" s="5" t="inlineStr">
+        <is>
+          <t>дыхание, РСЯ, t=19, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДЫХАНИЕ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 19</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="n"/>
+      <c r="D845" s="2" t="n"/>
+      <c r="E845" s="2" t="n"/>
+      <c r="F845" s="2" t="n"/>
+      <c r="G845" s="2" t="n"/>
+      <c r="H845" s="2" t="n"/>
+      <c r="I845" s="2" t="n"/>
+      <c r="J845" s="2" t="n"/>
+      <c r="K845" s="2" t="n"/>
+      <c r="L845" s="2" t="n"/>
+      <c r="M845" s="2" t="n"/>
+      <c r="N845" s="3" t="n"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="4" t="inlineStr">
+        <is>
+          <t>Тег 15:00:</t>
+        </is>
+      </c>
+      <c r="B846" s="5" t="inlineStr">
+        <is>
+          <t>дыхание, РСЯ, t=15, АВ Автоворонка, АВ Этап: Оплата, АВ Продукт: ДЫХАНИЕ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ, АВ Время: 15</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="n"/>
+      <c r="D846" s="2" t="n"/>
+      <c r="E846" s="2" t="n"/>
+      <c r="F846" s="2" t="n"/>
+      <c r="G846" s="2" t="n"/>
+      <c r="H846" s="2" t="n"/>
+      <c r="I846" s="2" t="n"/>
+      <c r="J846" s="2" t="n"/>
+      <c r="K846" s="2" t="n"/>
+      <c r="L846" s="2" t="n"/>
+      <c r="M846" s="2" t="n"/>
+      <c r="N846" s="3" t="n"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="4" t="inlineStr">
+        <is>
+          <t>Теги регистрации:</t>
+        </is>
+      </c>
+      <c r="B847" s="5" t="inlineStr">
+        <is>
+          <t>Регистрация, Яндекс Реклама новый ленд, РСЯ, НИМБ, ДЫХАНИЕ, АВ Автоворонка, АВ Этап: Регистрация, АВ Продукт: ДЫХАНИЕ, АВ Канал: Яндекс, АВ Направление: РСЯ, АВ Подрядчик: НИМБ</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="n"/>
+      <c r="D847" s="2" t="n"/>
+      <c r="E847" s="2" t="n"/>
+      <c r="F847" s="2" t="n"/>
+      <c r="G847" s="2" t="n"/>
+      <c r="H847" s="2" t="n"/>
+      <c r="I847" s="2" t="n"/>
+      <c r="J847" s="2" t="n"/>
+      <c r="K847" s="2" t="n"/>
+      <c r="L847" s="2" t="n"/>
+      <c r="M847" s="2" t="n"/>
+      <c r="N847" s="3" t="n"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="4" t="inlineStr">
+        <is>
+          <t>Лист:</t>
+        </is>
+      </c>
+      <c r="B848" s="5" t="inlineStr">
+        <is>
+          <t>ДЫХАНИЕ</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="n"/>
+      <c r="D848" s="2" t="n"/>
+      <c r="E848" s="2" t="n"/>
+      <c r="F848" s="2" t="n"/>
+      <c r="G848" s="2" t="n"/>
+      <c r="H848" s="2" t="n"/>
+      <c r="I848" s="2" t="n"/>
+      <c r="J848" s="2" t="n"/>
+      <c r="K848" s="2" t="n"/>
+      <c r="L848" s="2" t="n"/>
+      <c r="M848" s="2" t="n"/>
+      <c r="N848" s="3" t="n"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="4" t="inlineStr">
+        <is>
+          <t>Посадочная:</t>
+        </is>
+      </c>
+      <c r="B849" s="5" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dih/rsya/a</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="n"/>
+      <c r="D849" s="2" t="n"/>
+      <c r="E849" s="2" t="n"/>
+      <c r="F849" s="2" t="n"/>
+      <c r="G849" s="2" t="n"/>
+      <c r="H849" s="2" t="n"/>
+      <c r="I849" s="2" t="n"/>
+      <c r="J849" s="2" t="n"/>
+      <c r="K849" s="2" t="n"/>
+      <c r="L849" s="2" t="n"/>
+      <c r="M849" s="2" t="n"/>
+      <c r="N849" s="3" t="n"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="4" t="inlineStr">
+        <is>
+          <t>Дата старта:</t>
+        </is>
+      </c>
+      <c r="B850" s="5" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="n"/>
+      <c r="D850" s="2" t="n"/>
+      <c r="E850" s="2" t="n"/>
+      <c r="F850" s="2" t="n"/>
+      <c r="G850" s="2" t="n"/>
+      <c r="H850" s="2" t="n"/>
+      <c r="I850" s="2" t="n"/>
+      <c r="J850" s="2" t="n"/>
+      <c r="K850" s="2" t="n"/>
+      <c r="L850" s="2" t="n"/>
+      <c r="M850" s="2" t="n"/>
+      <c r="N850" s="3" t="n"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="4" t="inlineStr">
+        <is>
+          <t>Дашборд продаж:</t>
+        </is>
+      </c>
+      <c r="B851" s="5" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/logic/funnel/update?id=1680871</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="n"/>
+      <c r="D851" s="2" t="n"/>
+      <c r="E851" s="2" t="n"/>
+      <c r="F851" s="2" t="n"/>
+      <c r="G851" s="2" t="n"/>
+      <c r="H851" s="2" t="n"/>
+      <c r="I851" s="2" t="n"/>
+      <c r="J851" s="2" t="n"/>
+      <c r="K851" s="2" t="n"/>
+      <c r="L851" s="2" t="n"/>
+      <c r="M851" s="2" t="n"/>
+      <c r="N851" s="3" t="n"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="4" t="inlineStr">
+        <is>
+          <t>Предсписок:</t>
+        </is>
+      </c>
+      <c r="B852" s="5" t="inlineStr">
+        <is>
+          <t>Нет предсписка</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="n"/>
+      <c r="D852" s="2" t="n"/>
+      <c r="E852" s="2" t="n"/>
+      <c r="F852" s="2" t="n"/>
+      <c r="G852" s="2" t="n"/>
+      <c r="H852" s="2" t="n"/>
+      <c r="I852" s="2" t="n"/>
+      <c r="J852" s="2" t="n"/>
+      <c r="K852" s="2" t="n"/>
+      <c r="L852" s="2" t="n"/>
+      <c r="M852" s="2" t="n"/>
+      <c r="N852" s="3" t="n"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="4" t="inlineStr">
+        <is>
+          <t>Реги общ ГК:</t>
+        </is>
+      </c>
+      <c r="B853" s="5" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=0&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2220.05.2022%22%2C%22to%22%3A%2224.05.2022%22%2C%22toNDays%22%3Anull%2C%22fromNDays%22%3Anull%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B8347430%5D%2C%22selected_tags%22%3A%5B%22%D0%B4%D1%8B%D1%85%D0%B0%D0%BD%D0%B8%D0%B5%22%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="n"/>
+      <c r="D853" s="2" t="n"/>
+      <c r="E853" s="2" t="n"/>
+      <c r="F853" s="2" t="n"/>
+      <c r="G853" s="2" t="n"/>
+      <c r="H853" s="2" t="n"/>
+      <c r="I853" s="2" t="n"/>
+      <c r="J853" s="2" t="n"/>
+      <c r="K853" s="2" t="n"/>
+      <c r="L853" s="2" t="n"/>
+      <c r="M853" s="2" t="n"/>
+      <c r="N853" s="3" t="n"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="4" t="inlineStr">
+        <is>
+          <t>Реги на 15:00:</t>
+        </is>
+      </c>
+      <c r="B854" s="5" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=0&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A5002734%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+15%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2215.07.2024%22%2C%22to%22%3A%2215.07.2024%22%2C%22toNDays%22%3Anull%2C%22fromNDays%22%3Anull%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B8347430%5D%2C%22selected_tags%22%3A%5B%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="n"/>
+      <c r="D854" s="2" t="n"/>
+      <c r="E854" s="2" t="n"/>
+      <c r="F854" s="2" t="n"/>
+      <c r="G854" s="2" t="n"/>
+      <c r="H854" s="2" t="n"/>
+      <c r="I854" s="2" t="n"/>
+      <c r="J854" s="2" t="n"/>
+      <c r="K854" s="2" t="n"/>
+      <c r="L854" s="2" t="n"/>
+      <c r="M854" s="2" t="n"/>
+      <c r="N854" s="3" t="n"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="4" t="inlineStr">
+        <is>
+          <t>Реги на 19:00:</t>
+        </is>
+      </c>
+      <c r="B855" s="5" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/user/user/index?uc%5Bsegment_id%5D=0&amp;uc%5Brule_string%5D=%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22UserContext_formfieldvalue%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AFormFieldValueRule%22%2C%22params%22%3A%7B%22valueMode%22%3A2%2C%22fieldId%22%3A5002734%2C%22fieldValue%22%3A%7B%22selected_id%22%3A%5B%22%D0%A3%D0%B4%D0%BE%D0%B1%D0%BD%D0%BE+%D1%81%D0%BC%D0%BE%D1%82%D1%80%D0%B5%D1%82%D1%8C+%D0%B2+19%3A00%22%5D%7D%2C%22caseSensitive%22%3Afalse%7D%7D%2C%7B%22type%22%3A%22user_hasdealrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Auser%3A%3Amodels%3A%3Arule%3A%3AHasDealRule%22%2C%22params%22%3A%7B%22linkedRule%22%3A%7B%22type%22%3A%22andrule%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3AAndRule%22%2C%22params%22%3A%7B%22children%22%3A%5B%7B%22type%22%3A%22deal_created_at%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Amodules%3A%3Asales%3A%3Arules%3A%3ADealCreatedAtRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22from%22%3A%2215.07.2024%22%2C%22to%22%3A%2215.07.2024%22%2C%22toNDays%22%3Anull%2C%22fromNDays%22%3Anull%2C%22dateType%22%3A%22prev_day%22%2C%22withTime%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%2C%7B%22type%22%3A%22deal_offer_id%22%2C%22inverted%22%3A0%2C%22className%22%3A%22app%3A%3Acomponents%3A%3Alogic%3A%3Arule%3A%3Asales%3A%3AOfferIdDealContextRule%22%2C%22params%22%3A%7B%22value%22%3A%7B%22selected_id%22%3A%5B8347430%5D%2C%22selected_tags%22%3A%5B%5D%2C%22all_object_with_tags%22%3Afalse%7D%2C%22valueMode%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D%2C%22countCondition%22%3Anull%7D%7D%5D%2C%22mode%22%3A%22and%22%7D%7D&amp;formParams%5Bclarity_uid%5D=wIMVGIqMM-l54Ric6Z1s6gW9Zhwq0Vn1</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="n"/>
+      <c r="D855" s="2" t="n"/>
+      <c r="E855" s="2" t="n"/>
+      <c r="F855" s="2" t="n"/>
+      <c r="G855" s="2" t="n"/>
+      <c r="H855" s="2" t="n"/>
+      <c r="I855" s="2" t="n"/>
+      <c r="J855" s="2" t="n"/>
+      <c r="K855" s="2" t="n"/>
+      <c r="L855" s="2" t="n"/>
+      <c r="M855" s="2" t="n"/>
+      <c r="N855" s="3" t="n"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="6" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B856" s="6" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="C856" s="6" t="inlineStr">
+        <is>
+          <t>Комната GC (аналит.)</t>
+        </is>
+      </c>
+      <c r="D856" s="6" t="inlineStr">
+        <is>
+          <t>Комната Web (вебинар)</t>
+        </is>
+      </c>
+      <c r="E856" s="6" t="inlineStr">
+        <is>
+          <t>Длительность</t>
+        </is>
+      </c>
+      <c r="F856" s="6" t="inlineStr">
+        <is>
+          <t>Повтор</t>
+        </is>
+      </c>
+      <c r="G856" s="6" t="inlineStr">
+        <is>
+          <t>Продажная</t>
+        </is>
+      </c>
+      <c r="H856" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+      <c r="I856" s="6" t="inlineStr">
+        <is>
+          <t>Тарифы ГК</t>
+        </is>
+      </c>
+      <c r="J856" s="6" t="inlineStr">
+        <is>
+          <t>OTO</t>
+        </is>
+      </c>
+      <c r="K856" s="6" t="inlineStr">
+        <is>
+          <t>Бонусы / Программа</t>
+        </is>
+      </c>
+      <c r="L856" s="6" t="inlineStr">
+        <is>
+          <t>GetCourse / Salebot</t>
+        </is>
+      </c>
+      <c r="M856" s="6" t="inlineStr">
+        <is>
+          <t>Condition / Калькулятор</t>
+        </is>
+      </c>
+      <c r="N856" s="6" t="inlineStr">
+        <is>
+          <t>BotHelp condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B857" s="7" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C857" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih1-19-rsya</t>
+        </is>
+      </c>
+      <c r="D857" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih1-19-rsya</t>
+        </is>
+      </c>
+      <c r="E857" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 40м</t>
+        </is>
+      </c>
+      <c r="F857" s="7" t="inlineStr"/>
+      <c r="G857" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dih/tarif-19-rsya</t>
+        </is>
+      </c>
+      <c r="H857" s="7" t="inlineStr"/>
+      <c r="I857" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih/tarif/curator-19-rsya</t>
+        </is>
+      </c>
+      <c r="J857" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih/oto-19-rsya</t>
+        </is>
+      </c>
+      <c r="K857" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/av/dih/bonus-1</t>
+        </is>
+      </c>
+      <c r="L857" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/update?id=2451609</t>
+        </is>
+      </c>
+      <c r="M857" s="7" t="inlineStr"/>
+      <c r="N857" s="7" t="inlineStr">
+        <is>
+          <t>воронка геткурс</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B858" s="7" t="inlineStr">
+        <is>
+          <t>2 день</t>
+        </is>
+      </c>
+      <c r="C858" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih2-19-rsya</t>
+        </is>
+      </c>
+      <c r="D858" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih2-19-rsya</t>
+        </is>
+      </c>
+      <c r="E858" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 17м</t>
+        </is>
+      </c>
+      <c r="F858" s="7" t="inlineStr"/>
+      <c r="G858" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dih/tarifz-19-rsya</t>
+        </is>
+      </c>
+      <c r="H858" s="7" t="inlineStr">
+        <is>
+          <t>тарифы с записью 2,3 дня</t>
+        </is>
+      </c>
+      <c r="I858" s="7" t="inlineStr"/>
+      <c r="J858" s="7" t="inlineStr"/>
+      <c r="K858" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/av/dih/bonus-2</t>
+        </is>
+      </c>
+      <c r="L858" s="7" t="inlineStr"/>
+      <c r="M858" s="8" t="n"/>
+      <c r="N858" s="8" t="n"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B859" s="7" t="inlineStr">
+        <is>
+          <t>3 день</t>
+        </is>
+      </c>
+      <c r="C859" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih3-19-rsya</t>
+        </is>
+      </c>
+      <c r="D859" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih3-19-rsya</t>
+        </is>
+      </c>
+      <c r="E859" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 23м</t>
+        </is>
+      </c>
+      <c r="F859" s="7" t="inlineStr"/>
+      <c r="G859" s="7" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dih/tarifz-19-rsya</t>
+        </is>
+      </c>
+      <c r="H859" s="7" t="inlineStr">
+        <is>
+          <t>тарифы с записью 2,3 дня</t>
+        </is>
+      </c>
+      <c r="I859" s="7" t="inlineStr"/>
+      <c r="J859" s="7" t="inlineStr"/>
+      <c r="K859" s="7" t="inlineStr"/>
+      <c r="L859" s="7" t="inlineStr"/>
+      <c r="M859" s="8" t="n"/>
+      <c r="N859" s="8" t="n"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B860" s="7" t="inlineStr">
+        <is>
+          <t>4 день</t>
+        </is>
+      </c>
+      <c r="C860" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih4-19-rsya</t>
+        </is>
+      </c>
+      <c r="D860" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih4-19-rsya</t>
+        </is>
+      </c>
+      <c r="E860" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 30м</t>
+        </is>
+      </c>
+      <c r="F860" s="7" t="inlineStr"/>
+      <c r="G860" s="7" t="inlineStr"/>
+      <c r="H860" s="7" t="inlineStr"/>
+      <c r="I860" s="7" t="inlineStr"/>
+      <c r="J860" s="7" t="inlineStr"/>
+      <c r="K860" s="7" t="inlineStr"/>
+      <c r="L860" s="7" t="inlineStr"/>
+      <c r="M860" s="8" t="n"/>
+      <c r="N860" s="8" t="n"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B861" s="7" t="inlineStr">
+        <is>
+          <t>5 день</t>
+        </is>
+      </c>
+      <c r="C861" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih5-19-rsya</t>
+        </is>
+      </c>
+      <c r="D861" s="7" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih5-19-rsya</t>
+        </is>
+      </c>
+      <c r="E861" s="7" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 53м</t>
+        </is>
+      </c>
+      <c r="F861" s="7" t="inlineStr"/>
+      <c r="G861" s="7" t="inlineStr"/>
+      <c r="H861" s="7" t="inlineStr"/>
+      <c r="I861" s="7" t="inlineStr"/>
+      <c r="J861" s="7" t="inlineStr"/>
+      <c r="K861" s="7" t="inlineStr">
+        <is>
+          <t>геткурс</t>
+        </is>
+      </c>
+      <c r="L861" s="7" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/pl/tasks/mission/process?id=2456727</t>
+        </is>
+      </c>
+      <c r="M861" s="9" t="n"/>
+      <c r="N861" s="8" t="n"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B862" s="10" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C862" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih1-15-rsya</t>
+        </is>
+      </c>
+      <c r="D862" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih1-15-rsya</t>
+        </is>
+      </c>
+      <c r="E862" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 1ч 40м</t>
+        </is>
+      </c>
+      <c r="F862" s="10" t="inlineStr"/>
+      <c r="G862" s="10" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dih/tarif-15-rsya</t>
+        </is>
+      </c>
+      <c r="H862" s="10" t="inlineStr"/>
+      <c r="I862" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih/tarif/curator-15-rsya</t>
+        </is>
+      </c>
+      <c r="J862" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih/oto-15-rsya</t>
+        </is>
+      </c>
+      <c r="K862" s="10" t="inlineStr"/>
+      <c r="L862" s="10" t="inlineStr"/>
+      <c r="M862" s="10" t="inlineStr"/>
+      <c r="N862" s="8" t="n"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B863" s="10" t="inlineStr">
+        <is>
+          <t>2 день</t>
+        </is>
+      </c>
+      <c r="C863" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih2-15-rsya</t>
+        </is>
+      </c>
+      <c r="D863" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih2-15-rsya</t>
+        </is>
+      </c>
+      <c r="E863" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 17м</t>
+        </is>
+      </c>
+      <c r="F863" s="10" t="inlineStr"/>
+      <c r="G863" s="10" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dih/tarifz-15-rsya</t>
+        </is>
+      </c>
+      <c r="H863" s="10" t="inlineStr">
+        <is>
+          <t>тарифы с записью 2,3 дня</t>
+        </is>
+      </c>
+      <c r="I863" s="10" t="inlineStr"/>
+      <c r="J863" s="10" t="inlineStr"/>
+      <c r="K863" s="10" t="inlineStr"/>
+      <c r="L863" s="10" t="inlineStr"/>
+      <c r="M863" s="8" t="n"/>
+      <c r="N863" s="8" t="n"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B864" s="10" t="inlineStr">
+        <is>
+          <t>3 день</t>
+        </is>
+      </c>
+      <c r="C864" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih3-15-rsya</t>
+        </is>
+      </c>
+      <c r="D864" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih3-15-rsya</t>
+        </is>
+      </c>
+      <c r="E864" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 23м</t>
+        </is>
+      </c>
+      <c r="F864" s="10" t="inlineStr"/>
+      <c r="G864" s="10" t="inlineStr">
+        <is>
+          <t>https://t.ksamata.ru/dih/tarifz-15-rsya</t>
+        </is>
+      </c>
+      <c r="H864" s="10" t="inlineStr">
+        <is>
+          <t>тарифы с записью 2,3 дня</t>
+        </is>
+      </c>
+      <c r="I864" s="10" t="inlineStr"/>
+      <c r="J864" s="10" t="inlineStr"/>
+      <c r="K864" s="10" t="inlineStr"/>
+      <c r="L864" s="10" t="inlineStr"/>
+      <c r="M864" s="8" t="n"/>
+      <c r="N864" s="8" t="n"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B865" s="10" t="inlineStr">
+        <is>
+          <t>4 день</t>
+        </is>
+      </c>
+      <c r="C865" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih4-15-rsya</t>
+        </is>
+      </c>
+      <c r="D865" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih4-15-rsya</t>
+        </is>
+      </c>
+      <c r="E865" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 30м</t>
+        </is>
+      </c>
+      <c r="F865" s="10" t="inlineStr"/>
+      <c r="G865" s="10" t="inlineStr"/>
+      <c r="H865" s="10" t="inlineStr"/>
+      <c r="I865" s="10" t="inlineStr"/>
+      <c r="J865" s="10" t="inlineStr"/>
+      <c r="K865" s="10" t="inlineStr"/>
+      <c r="L865" s="10" t="inlineStr"/>
+      <c r="M865" s="8" t="n"/>
+      <c r="N865" s="8" t="n"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B866" s="10" t="inlineStr">
+        <is>
+          <t>5 день</t>
+        </is>
+      </c>
+      <c r="C866" s="10" t="inlineStr">
+        <is>
+          <t>https://gc.ksamata.ru/dih5-15-rsya</t>
+        </is>
+      </c>
+      <c r="D866" s="10" t="inlineStr">
+        <is>
+          <t>https://web.ksamatacenter.com/room/dih5-15-rsya</t>
+        </is>
+      </c>
+      <c r="E866" s="10" t="inlineStr">
+        <is>
+          <t>⏱ 2ч 53м</t>
+        </is>
+      </c>
+      <c r="F866" s="10" t="inlineStr"/>
+      <c r="G866" s="10" t="inlineStr"/>
+      <c r="H866" s="10" t="inlineStr"/>
+      <c r="I866" s="10" t="inlineStr"/>
+      <c r="J866" s="10" t="inlineStr"/>
+      <c r="K866" s="10" t="inlineStr"/>
+      <c r="L866" s="10" t="inlineStr"/>
+      <c r="M866" s="9" t="n"/>
+      <c r="N866" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="581">
+  <mergeCells count="599">
     <mergeCell ref="B308:N308"/>
     <mergeCell ref="B379:N379"/>
     <mergeCell ref="M158:M162"/>
@@ -27655,6 +28533,7 @@
     <mergeCell ref="B326:N326"/>
     <mergeCell ref="B513:N513"/>
     <mergeCell ref="B684:N684"/>
+    <mergeCell ref="B847:N847"/>
     <mergeCell ref="B152:N152"/>
     <mergeCell ref="B748:N748"/>
     <mergeCell ref="B686:N686"/>
@@ -27665,6 +28544,7 @@
     <mergeCell ref="B550:N550"/>
     <mergeCell ref="B606:N606"/>
     <mergeCell ref="B544:N544"/>
+    <mergeCell ref="B848:N848"/>
     <mergeCell ref="B283:N283"/>
     <mergeCell ref="B87:N87"/>
     <mergeCell ref="B519:N519"/>
@@ -27709,6 +28589,7 @@
     <mergeCell ref="B627:N627"/>
     <mergeCell ref="B316:N316"/>
     <mergeCell ref="M804:M808"/>
+    <mergeCell ref="B850:N850"/>
     <mergeCell ref="B95:N95"/>
     <mergeCell ref="B89:N89"/>
     <mergeCell ref="B331:N331"/>
@@ -27723,6 +28604,7 @@
     <mergeCell ref="B224:N224"/>
     <mergeCell ref="B693:N693"/>
     <mergeCell ref="B72:N72"/>
+    <mergeCell ref="B845:N845"/>
     <mergeCell ref="B90:N90"/>
     <mergeCell ref="B655:N655"/>
     <mergeCell ref="B184:N184"/>
@@ -27747,6 +28629,7 @@
     <mergeCell ref="B602:N602"/>
     <mergeCell ref="B746:N746"/>
     <mergeCell ref="B540:N540"/>
+    <mergeCell ref="B844:N844"/>
     <mergeCell ref="B254:N254"/>
     <mergeCell ref="B143:N143"/>
     <mergeCell ref="B490:N490"/>
@@ -27771,6 +28654,7 @@
     <mergeCell ref="B259:N259"/>
     <mergeCell ref="B459:N459"/>
     <mergeCell ref="B630:N630"/>
+    <mergeCell ref="B853:N853"/>
     <mergeCell ref="B98:N98"/>
     <mergeCell ref="B225:N225"/>
     <mergeCell ref="B274:N274"/>
@@ -27804,6 +28688,7 @@
     <mergeCell ref="B86:N86"/>
     <mergeCell ref="M107:M111"/>
     <mergeCell ref="A681:N681"/>
+    <mergeCell ref="B849:N849"/>
     <mergeCell ref="N262:N271"/>
     <mergeCell ref="B182:N182"/>
     <mergeCell ref="B467:N467"/>
@@ -27864,6 +28749,7 @@
     <mergeCell ref="B694:N694"/>
     <mergeCell ref="A221:N221"/>
     <mergeCell ref="B581:N581"/>
+    <mergeCell ref="N857:N866"/>
     <mergeCell ref="N102:N111"/>
     <mergeCell ref="B768:N768"/>
     <mergeCell ref="B817:N817"/>
@@ -27876,15 +28762,18 @@
     <mergeCell ref="B639:N639"/>
     <mergeCell ref="B577:N577"/>
     <mergeCell ref="B797:N797"/>
+    <mergeCell ref="M862:M866"/>
     <mergeCell ref="B278:N278"/>
     <mergeCell ref="B405:N405"/>
     <mergeCell ref="B799:N799"/>
     <mergeCell ref="B171:N171"/>
     <mergeCell ref="B407:N407"/>
     <mergeCell ref="B578:N578"/>
+    <mergeCell ref="M857:M861"/>
     <mergeCell ref="B515:N515"/>
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="B438:N438"/>
+    <mergeCell ref="A841:N841"/>
     <mergeCell ref="A349:N349"/>
     <mergeCell ref="B6:N6"/>
     <mergeCell ref="B204:N204"/>
@@ -27913,6 +28802,7 @@
     <mergeCell ref="B228:N228"/>
     <mergeCell ref="N642:N651"/>
     <mergeCell ref="N473:N482"/>
+    <mergeCell ref="B843:N843"/>
     <mergeCell ref="B88:N88"/>
     <mergeCell ref="A789:N789"/>
     <mergeCell ref="B818:N818"/>
@@ -27962,6 +28852,7 @@
     <mergeCell ref="B154:N154"/>
     <mergeCell ref="M318:M320"/>
     <mergeCell ref="N214:N219"/>
+    <mergeCell ref="B846:N846"/>
     <mergeCell ref="B91:N91"/>
     <mergeCell ref="N46:N55"/>
     <mergeCell ref="B156:N156"/>
@@ -28009,6 +28900,7 @@
     <mergeCell ref="B600:N600"/>
     <mergeCell ref="B404:N404"/>
     <mergeCell ref="B771:N771"/>
+    <mergeCell ref="B842:N842"/>
     <mergeCell ref="B252:N252"/>
     <mergeCell ref="B208:N208"/>
     <mergeCell ref="M102:M106"/>
@@ -28021,6 +28913,7 @@
     <mergeCell ref="B170:N170"/>
     <mergeCell ref="A373:N373"/>
     <mergeCell ref="A815:N815"/>
+    <mergeCell ref="B852:N852"/>
     <mergeCell ref="M191:M195"/>
     <mergeCell ref="M262:M266"/>
     <mergeCell ref="B333:N333"/>
@@ -28035,6 +28928,7 @@
     <mergeCell ref="M783:M787"/>
     <mergeCell ref="A735:N735"/>
     <mergeCell ref="B99:N99"/>
+    <mergeCell ref="B854:N854"/>
     <mergeCell ref="B568:N568"/>
     <mergeCell ref="B457:N457"/>
     <mergeCell ref="B257:N257"/>
@@ -28044,6 +28938,7 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B766:N766"/>
     <mergeCell ref="B486:N486"/>
+    <mergeCell ref="B855:N855"/>
     <mergeCell ref="B94:N94"/>
     <mergeCell ref="A762:N762"/>
     <mergeCell ref="N445:N454"/>
@@ -28116,6 +29011,7 @@
     <mergeCell ref="B286:N286"/>
     <mergeCell ref="B553:N553"/>
     <mergeCell ref="N556:N565"/>
+    <mergeCell ref="B851:N851"/>
     <mergeCell ref="B690:N690"/>
     <mergeCell ref="A301:N301"/>
     <mergeCell ref="A57:N57"/>
